--- a/results-summarized/summary-Czech2-morf-xsk.xlsx
+++ b/results-summarized/summary-Czech2-morf-xsk.xlsx
@@ -5,20 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kowk/Dropbox/GitHub/ngram-based-noun-classification/results-Morfessor/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kowk/Dropbox/GitHub/ngram-based-noun-classification/results-summarized/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D50799-2B2D-3D49-89F8-CF75D1BA0B7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03C41624-B93C-ED42-A745-DF3FCC174DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4400" yWindow="500" windowWidth="28660" windowHeight="17900" activeTab="2" xr2:uid="{6163965D-BEB7-DE4E-9942-5490D3BDCDC8}"/>
+    <workbookView xWindow="4940" yWindow="720" windowWidth="28660" windowHeight="17900" activeTab="4" xr2:uid="{6163965D-BEB7-DE4E-9942-5490D3BDCDC8}"/>
   </bookViews>
   <sheets>
     <sheet name="summarized" sheetId="7" r:id="rId1"/>
-    <sheet name="summarized.old" sheetId="4" r:id="rId2"/>
-    <sheet name="2.0k-ml3.0-xsk-mgv9" sheetId="6" r:id="rId3"/>
-    <sheet name="2.0k-ml2.0-xsk-mgv9" sheetId="1" r:id="rId4"/>
-    <sheet name="1.2k-ml3.0-xsk-mgv9" sheetId="5" r:id="rId5"/>
-    <sheet name="1.2k-ml2.0-xsk-mgv9" sheetId="3" r:id="rId6"/>
+    <sheet name="2.0k-ml3.0-xsk-mgv9" sheetId="6" r:id="rId2"/>
+    <sheet name="2.0k-ml2.0-xsk-mgv9" sheetId="1" r:id="rId3"/>
+    <sheet name="1.2k-ml3.0-xsk-mgv9" sheetId="5" r:id="rId4"/>
+    <sheet name="1.2k-ml2.0-xsk-mgv9" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="40">
   <si>
     <t>lang</t>
   </si>
@@ -158,9 +157,6 @@
     <t>max.rank</t>
   </si>
   <si>
-    <t>sample</t>
-  </si>
-  <si>
     <t>ml</t>
   </si>
   <si>
@@ -189,9 +185,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="18">
     <font>
@@ -312,7 +307,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -494,30 +489,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor theme="4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor auto="1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="65"/>
-        <bgColor auto="1"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="16">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -652,46 +629,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </right>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -737,37 +674,17 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="34" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="13" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="36" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="36" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -813,7 +730,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="193">
+  <dxfs count="143">
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
@@ -2507,437 +2424,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <right style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </right>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="LucidaSansUnicode"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <right style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </right>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="13"/>
-        <color theme="0"/>
-        <name val="LucidaSansUnicode"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <right style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </right>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="LucidaSansUnicode"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <right style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </right>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="13"/>
-        <color theme="0"/>
-        <name val="LucidaSansUnicode"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <right style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </right>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="LucidaSansUnicode"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill>
-          <fgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <fill>
-        <patternFill>
-          <fgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <right style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </right>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="13"/>
-        <color theme="0"/>
-        <name val="LucidaSansUnicode"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right/>
@@ -5788,2478 +5274,6 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP"/>
-              <a:t>Czech</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="ja-JP" altLang="en-US"/>
-              <a:t> </a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP"/>
-              <a:t>plurality</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="ja-JP" altLang="en-US" baseline="0"/>
-              <a:t> </a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP" baseline="0"/>
-              <a:t>with</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="ja-JP" altLang="en-US" baseline="0"/>
-              <a:t> </a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP" baseline="0"/>
-              <a:t>Morfessor</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="ja-JP" altLang="en-US" baseline="0"/>
-              <a:t> </a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP" baseline="0"/>
-              <a:t>segmentations</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-JP"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>summarized.old!$I$2</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>ml2-2k-Czech-plurality-suppl:TRUE</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>summarized.old!$J$1:$V$1</c:f>
-              <c:strCache>
-                <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>2g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>xsk2g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>xsk3g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>xsk4g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>3g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>4g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>xsk2g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>xsk3g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>xsk4g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>max</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>summarized.old!$J$2:$V$2</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>0.94</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.86</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.91</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.88</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.83</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.89</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.9</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.83</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.85</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.85</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.81</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.84</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.94</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D3F9-2440-AC5A-CF30E44B99E2}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>summarized.old!$I$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>ml2-1.2k-Czech-plurality-suppl:TRUE</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>summarized.old!$J$1:$V$1</c:f>
-              <c:strCache>
-                <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>2g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>xsk2g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>xsk3g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>xsk4g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>3g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>4g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>xsk2g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>xsk3g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>xsk4g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>max</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>summarized.old!$J$3:$V$3</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>0.87</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.83</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.86</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.86</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.84</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.82</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.89</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.84</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.88</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.84</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.85</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.8</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.89</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-D3F9-2440-AC5A-CF30E44B99E2}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>summarized.old!$I$4</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>ml3-2k-Czech-plurality-suppl:TRUE</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>summarized.old!$J$1:$V$1</c:f>
-              <c:strCache>
-                <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>2g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>xsk2g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>xsk3g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>xsk4g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>3g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>4g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>xsk2g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>xsk3g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>xsk4g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>max</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>summarized.old!$J$4:$V$4</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>0.92</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.89</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.83</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.88</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.88</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.88</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.88</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.88</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.89</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.84</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.86</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.87</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.92</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-D3F9-2440-AC5A-CF30E44B99E2}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>summarized.old!$I$5</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>ml3-1.2k-Czech-plurality-suppl:TRUE</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>summarized.old!$J$1:$V$1</c:f>
-              <c:strCache>
-                <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>2g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>xsk2g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>xsk3g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>xsk4g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>3g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>4g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>xsk2g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>xsk3g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>xsk4g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>max</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>summarized.old!$J$5:$V$5</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>0.91</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.88</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.87</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.88</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.9</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.85</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.88</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.87</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.86</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.86</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.85</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.82</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.91</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-D3F9-2440-AC5A-CF30E44B99E2}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:smooth val="0"/>
-        <c:axId val="1687598335"/>
-        <c:axId val="1358815471"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="1687598335"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-JP"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1358815471"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1358815471"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="0.00" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-JP"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1687598335"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-JP"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-JP"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP"/>
-              <a:t>Czech</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="ja-JP" altLang="en-US" baseline="0"/>
-              <a:t> </a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP" baseline="0"/>
-              <a:t>gender</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="ja-JP" altLang="en-US" baseline="0"/>
-              <a:t> </a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP" baseline="0"/>
-              <a:t>with</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="ja-JP" altLang="en-US" baseline="0"/>
-              <a:t> </a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP" baseline="0"/>
-              <a:t>Morfessor</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="ja-JP" altLang="en-US" baseline="0"/>
-              <a:t> </a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP" baseline="0"/>
-              <a:t>segmentations</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-JP"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>summarized.old!$I$16</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>ml2-2k-Czech-gender-suppl:TRUE</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>summarized.old!$J$15:$V$15</c:f>
-              <c:strCache>
-                <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>2g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>xsk2g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>xsk3g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>xsk4g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>3g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>4g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>xsk2g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>xsk3g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>xsk4g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>max</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>summarized.old!$J$16:$V$16</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>0.62</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.56999999999999995</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.62</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.62</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.56999999999999995</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.69</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.64</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.6</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.54</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.61</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.68</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.6</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.69</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C4C0-8344-A436-59317F8682BB}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>summarized.old!$I$17</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>ml2-1.2k-Czech-gender-suppl:TRUE</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>summarized.old!$J$15:$V$15</c:f>
-              <c:strCache>
-                <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>2g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>xsk2g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>xsk3g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>xsk4g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>3g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>4g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>xsk2g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>xsk3g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>xsk4g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>max</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>summarized.old!$J$17:$V$17</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>0.62</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.56999999999999995</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.62</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.62</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.56999999999999995</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.69</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.64</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.6</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.54</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.61</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.68</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.6</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.69</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-C4C0-8344-A436-59317F8682BB}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>summarized.old!$I$18</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>ml3-2k-Czech-gender-suppl:TRUE</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>summarized.old!$J$15:$V$15</c:f>
-              <c:strCache>
-                <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>2g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>xsk2g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>xsk3g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>xsk4g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>3g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>4g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>xsk2g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>xsk3g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>xsk4g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>max</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>summarized.old!$J$18:$V$18</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>0.7</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.66</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.7</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.65</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.68</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.62</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.71</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.71</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.66</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.68</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.64</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.69</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.71</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-C4C0-8344-A436-59317F8682BB}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>summarized.old!$I$19</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>ml3-1.2k-Czech-gender-suppl:TRUE</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>summarized.old!$J$15:$V$15</c:f>
-              <c:strCache>
-                <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>2g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>xsk2g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>xsk3g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>xsk4g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>3g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>4g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>xsk2g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>xsk3g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>xsk4g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>max</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>summarized.old!$J$19:$V$19</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>0.55000000000000004</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.57999999999999996</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.68</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.63</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.65</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.68</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.69</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.71</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.57999999999999996</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.51</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.71</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-C4C0-8344-A436-59317F8682BB}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:smooth val="0"/>
-        <c:axId val="1671960095"/>
-        <c:axId val="1672013935"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="1671960095"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-JP"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1672013935"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1672013935"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="0.00" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-JP"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1671960095"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-JP"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-JP"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP"/>
-              <a:t>Czech</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="ja-JP" altLang="en-US"/>
-              <a:t> </a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP"/>
-              <a:t>case</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="ja-JP" altLang="en-US"/>
-              <a:t> </a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP"/>
-              <a:t>with</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="ja-JP" altLang="en-US"/>
-              <a:t> </a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP"/>
-              <a:t>Morfessor</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="ja-JP" altLang="en-US"/>
-              <a:t> </a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ja-JP"/>
-              <a:t>segmentations</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-JP"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>summarized.old!$I$30</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>ml2-2k-Czech-case-suppl:TRUE</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>summarized.old!$J$29:$V$29</c:f>
-              <c:strCache>
-                <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>2g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>xsk2g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>xsk3g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>xsk4g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>3g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>4g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>xsk2g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>xsk3g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>xsk4g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>max</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>summarized.old!$J$30:$V$30</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>0.59</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.38</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.51</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.47</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.4</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.54</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.48</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.52</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.52</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.47</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.44</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.59</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-BE70-FC4E-B5DC-8CC262D495DB}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>summarized.old!$I$31</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>ml2-1.2k-Czech-case-suppl:TRUE</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>summarized.old!$J$29:$V$29</c:f>
-              <c:strCache>
-                <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>2g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>xsk2g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>xsk3g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>xsk4g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>3g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>4g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>xsk2g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>xsk3g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>xsk4g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>max</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>summarized.old!$J$31:$V$31</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>0.59</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.38</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.51</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.47</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.4</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.54</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.48</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.52</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.52</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.47</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.44</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.59</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-BE70-FC4E-B5DC-8CC262D495DB}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>summarized.old!$I$32</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>ml3-2k-Czech-case-suppl:TRUE</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>summarized.old!$J$29:$V$29</c:f>
-              <c:strCache>
-                <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>2g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>xsk2g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>xsk3g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>xsk4g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>3g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>4g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>xsk2g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>xsk3g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>xsk4g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>max</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>summarized.old!$J$32:$V$32</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>0.55000000000000004</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.53</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.56000000000000005</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.48</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.49</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.51</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.56999999999999995</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.56000000000000005</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.59</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.54</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.59</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-BE70-FC4E-B5DC-8CC262D495DB}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>summarized.old!$I$33</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>ml3-1.2k-Czech-case-suppl:TRUE</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>summarized.old!$J$29:$V$29</c:f>
-              <c:strCache>
-                <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>2g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>xsk2g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>xsk3g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>xsk4g-no-hash</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>3g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>4g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>xsk2g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>xsk3g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>xsk4g-hash-at-both</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>max</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>summarized.old!$J$33:$V$33</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>0.45</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.54</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.62</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.49</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.47</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.47</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.46</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.53</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.43</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.45</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.51</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.62</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-BE70-FC4E-B5DC-8CC262D495DB}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:smooth val="0"/>
-        <c:axId val="190145120"/>
-        <c:axId val="2136173647"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="190145120"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-JP"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="2136173647"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="2136173647"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="0.00" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-JP"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="190145120"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-JP"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-JP"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="12">
   <a:schemeClr val="accent2"/>
@@ -8297,1666 +5311,7 @@
 </cs:colorStyle>
 </file>
 
-<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="12">
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="12">
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="12">
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -10513,119 +5868,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>514350</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>190497</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>516850</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>297997</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BC956A3-288A-5623-4FA8-9DA1C36C78F8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>438150</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>133347</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>440650</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>240847</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ACBE6F04-96D9-6FA6-50D0-EB78CA5226E0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>476250</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>31747</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>478750</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>139247</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B7DB1BB-2859-AC08-6F1B-7FB03B59BBD4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{FF527EAE-4C73-494D-90B4-D491BD5C5C9E}" name="Table6" displayName="Table6" ref="A1:X25" totalsRowShown="0">
   <autoFilter ref="A1:X25" xr:uid="{FF527EAE-4C73-494D-90B4-D491BD5C5C9E}"/>
@@ -10643,283 +5885,28 @@
     <tableColumn id="7" xr3:uid="{4648D50A-FB13-E44B-95E1-43FCF2A4F513}" name="supplemented"/>
     <tableColumn id="8" xr3:uid="{4334E061-B655-104D-8EB1-7209EE94EB2F}" name="method.index"/>
     <tableColumn id="9" xr3:uid="{74842E72-E30D-7D41-9CAC-AA500F232E59}" name="metric"/>
-    <tableColumn id="1" xr3:uid="{77CACCB7-B169-5B43-A2B8-42EC4D09657F}" name="var" dataDxfId="192">
+    <tableColumn id="1" xr3:uid="{77CACCB7-B169-5B43-A2B8-42EC4D09657F}" name="var" dataDxfId="142">
       <calculatedColumnFormula>_xlfn.LET(_xlpm.ml,_xlfn.SINGLE(Table6[ml]),_xlpm.sn,_xlfn.SINGLE(Table6[sample.n]),_xlpm.spl,_xlfn.SINGLE(Table6[supplemented]),_xlpm.mgv,_xlfn.SINGLE(Table6[mgv]),_xlpm.attr,_xlfn.SINGLE(Table6[attribute]),_xlfn.TEXTJOIN({"-ml:","-suppl:","-mgv:","-sn:",""},TRUE,LEFT(_xlpm.attr,3),_xlpm.ml,LEFT(_xlpm.spl,1),_xlpm.mgv,_xlpm.sn,"k"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{A8BCAFFD-120A-0246-903F-1CE26DD82701}" name="2g-no-hash" dataDxfId="191"/>
-    <tableColumn id="11" xr3:uid="{1C09E473-F70D-D741-B647-9D21B9BFD98A}" name="3g-no-hash" dataDxfId="190"/>
-    <tableColumn id="12" xr3:uid="{5B61C2F3-B396-014D-94E9-EBC347C94CAF}" name="4g-no-hash" dataDxfId="189"/>
-    <tableColumn id="13" xr3:uid="{D918E075-42A2-F041-A846-8A3D47819EC1}" name="xsk2g-no-hash" dataDxfId="188"/>
-    <tableColumn id="14" xr3:uid="{C0F5BFB3-3F3F-C24F-86CF-39651B3341E0}" name="xsk3g-no-hash" dataDxfId="187"/>
-    <tableColumn id="15" xr3:uid="{B48A4C39-E946-2742-879C-B7D837B8479E}" name="xsk4g-no-hash" dataDxfId="186"/>
-    <tableColumn id="16" xr3:uid="{DF143273-6B20-AA47-B496-5A3939F548A3}" name="2g-hash-at-both" dataDxfId="185"/>
-    <tableColumn id="17" xr3:uid="{5C36DC09-68D5-9441-A49B-983B956D0624}" name="3g-hash-at-both" dataDxfId="184"/>
-    <tableColumn id="18" xr3:uid="{491C42AB-2DC7-514D-9A20-6F1818E653BA}" name="4g-hash-at-both" dataDxfId="183"/>
-    <tableColumn id="19" xr3:uid="{309E3C4A-2DF2-CF44-9EA9-9FF661EAC82D}" name="xsk2g-hash-at-both" dataDxfId="182"/>
-    <tableColumn id="20" xr3:uid="{E1C3A6C1-0D1B-9744-AD82-EE340F3B375E}" name="xsk3g-hash-at-both" dataDxfId="181"/>
-    <tableColumn id="21" xr3:uid="{B319CE29-4BCE-E74D-AAB3-A44B2F6870C3}" name="xsk4g-hash-at-both" dataDxfId="180"/>
-    <tableColumn id="22" xr3:uid="{B3142545-21CF-DF40-B492-D5101B77E63B}" name="max" dataDxfId="179"/>
+    <tableColumn id="10" xr3:uid="{A8BCAFFD-120A-0246-903F-1CE26DD82701}" name="2g-no-hash" dataDxfId="141"/>
+    <tableColumn id="11" xr3:uid="{1C09E473-F70D-D741-B647-9D21B9BFD98A}" name="3g-no-hash" dataDxfId="140"/>
+    <tableColumn id="12" xr3:uid="{5B61C2F3-B396-014D-94E9-EBC347C94CAF}" name="4g-no-hash" dataDxfId="139"/>
+    <tableColumn id="13" xr3:uid="{D918E075-42A2-F041-A846-8A3D47819EC1}" name="xsk2g-no-hash" dataDxfId="138"/>
+    <tableColumn id="14" xr3:uid="{C0F5BFB3-3F3F-C24F-86CF-39651B3341E0}" name="xsk3g-no-hash" dataDxfId="137"/>
+    <tableColumn id="15" xr3:uid="{B48A4C39-E946-2742-879C-B7D837B8479E}" name="xsk4g-no-hash" dataDxfId="136"/>
+    <tableColumn id="16" xr3:uid="{DF143273-6B20-AA47-B496-5A3939F548A3}" name="2g-hash-at-both" dataDxfId="135"/>
+    <tableColumn id="17" xr3:uid="{5C36DC09-68D5-9441-A49B-983B956D0624}" name="3g-hash-at-both" dataDxfId="134"/>
+    <tableColumn id="18" xr3:uid="{491C42AB-2DC7-514D-9A20-6F1818E653BA}" name="4g-hash-at-both" dataDxfId="133"/>
+    <tableColumn id="19" xr3:uid="{309E3C4A-2DF2-CF44-9EA9-9FF661EAC82D}" name="xsk2g-hash-at-both" dataDxfId="132"/>
+    <tableColumn id="20" xr3:uid="{E1C3A6C1-0D1B-9744-AD82-EE340F3B375E}" name="xsk3g-hash-at-both" dataDxfId="131"/>
+    <tableColumn id="21" xr3:uid="{B319CE29-4BCE-E74D-AAB3-A44B2F6870C3}" name="xsk4g-hash-at-both" dataDxfId="130"/>
+    <tableColumn id="22" xr3:uid="{B3142545-21CF-DF40-B492-D5101B77E63B}" name="max" dataDxfId="129"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AECC5072-F047-8B44-8BB6-96052FE91454}" name="Table1" displayName="Table1" ref="A1:S19" totalsRowShown="0">
-  <autoFilter ref="A1:S19" xr:uid="{AECC5072-F047-8B44-8BB6-96052FE91454}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S19">
-    <sortCondition ref="B1:B19"/>
-  </sortState>
-  <tableColumns count="19">
-    <tableColumn id="1" xr3:uid="{1327DC5E-DC70-8A4D-9B1F-3995AE90E6FD}" name="lang"/>
-    <tableColumn id="2" xr3:uid="{5EF94ABC-9242-3F46-B0A6-BF578616549F}" name="attribute.index"/>
-    <tableColumn id="3" xr3:uid="{7ABA1446-5876-F742-BFE2-C40E3818548C}" name="attribute"/>
-    <tableColumn id="4" xr3:uid="{57C4556B-D00C-D24E-BADF-6D97D0CA4318}" name="supplement"/>
-    <tableColumn id="5" xr3:uid="{988388D8-7223-204B-885D-63BE8FD231BA}" name="method.index"/>
-    <tableColumn id="6" xr3:uid="{B6E039AA-5879-304A-BF97-3FD1C15339DC}" name="method"/>
-    <tableColumn id="7" xr3:uid="{B547C5B4-5DE8-A540-9F99-C08EB5487E2F}" name="2g-no-hash" dataDxfId="102"/>
-    <tableColumn id="8" xr3:uid="{61EE02A8-7C51-254F-8C4A-F987370F31B4}" name="3g-no-hash" dataDxfId="101"/>
-    <tableColumn id="9" xr3:uid="{F7CEC792-9442-5845-B7FA-B7EB0C6BAFDB}" name="4g-no-hash" dataDxfId="100"/>
-    <tableColumn id="10" xr3:uid="{48A3ABF5-42C0-B247-966C-F76FC9295319}" name="xsk2g-no-hash" dataDxfId="99"/>
-    <tableColumn id="11" xr3:uid="{75523B27-FF4E-9041-B642-195593D373FD}" name="xsk3g-no-hash" dataDxfId="98"/>
-    <tableColumn id="12" xr3:uid="{CE927920-C222-0044-863A-CD6CCEAB0264}" name="xsk4g-no-hash" dataDxfId="97"/>
-    <tableColumn id="13" xr3:uid="{5355CE3B-D063-B74D-B6EE-829545E87A85}" name="2g-hash-at-both" dataDxfId="96"/>
-    <tableColumn id="14" xr3:uid="{5A4024C9-DD8A-344F-A354-E76F042BB0C4}" name="3g-hash-at-both" dataDxfId="95"/>
-    <tableColumn id="15" xr3:uid="{D0F84E10-490E-FC49-B941-5607004585D3}" name="4g-hash-at-both" dataDxfId="94"/>
-    <tableColumn id="16" xr3:uid="{0BC3C2D0-5994-B046-991C-31524C3441D2}" name="xsk2g-hash-at-both" dataDxfId="93"/>
-    <tableColumn id="17" xr3:uid="{3A798061-F077-CA49-859C-963FFBF75831}" name="xsk3g-hash-at-both" dataDxfId="92"/>
-    <tableColumn id="18" xr3:uid="{36B31AED-5A21-3849-9CEF-A3C4A9D16F62}" name="xsk4g-hash-at-both" dataDxfId="91"/>
-    <tableColumn id="19" xr3:uid="{D46E6BD6-2DB9-F94B-BE12-5609179FA557}" name="max" dataDxfId="90">
-      <calculatedColumnFormula>_xlfn.LET(_xlpm.d,$G2:$R2,MAX(_xlpm.d))</calculatedColumnFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{0692717F-4AD9-5A43-997B-DECCE73C02C3}" name="Table5" displayName="Table5" ref="B22:S28" totalsRowShown="0">
-  <autoFilter ref="B22:S28" xr:uid="{0692717F-4AD9-5A43-997B-DECCE73C02C3}"/>
-  <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{0A4D604F-F8C1-0B4B-90C6-EAE050C704E4}" name="attribute.index"/>
-    <tableColumn id="2" xr3:uid="{9D57305A-6224-C542-96F4-FBD9797D0BF6}" name="attribute"/>
-    <tableColumn id="3" xr3:uid="{ABC18CB5-FED7-464B-993D-7CA8FB4F071A}" name="supplemented"/>
-    <tableColumn id="4" xr3:uid="{847EC6B0-B5D5-F247-A98B-9ED19BC48F2A}" name="method.index"/>
-    <tableColumn id="5" xr3:uid="{0ECBE385-F3F8-C340-8178-A4CB9B4B23B7}" name="metric"/>
-    <tableColumn id="6" xr3:uid="{15590882-F724-4343-85D1-377170A0E8EE}" name="2g-no-hash" dataDxfId="89">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,G$2:G$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="7" xr3:uid="{A52E75AE-F946-5447-8299-5982E85CF780}" name="3g-no-hash" dataDxfId="88">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,H$2:H$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="8" xr3:uid="{CDC64800-2690-CF48-BD74-EC01BE5C66DC}" name="4g-no-hash" dataDxfId="87">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,I$2:I$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="9" xr3:uid="{82E7043E-D5FC-8F41-AA0B-8E3099E7D351}" name="xsk2g-no-hash" dataDxfId="86">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,J$2:J$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="10" xr3:uid="{DCA1203B-8423-0744-8464-5312746CD7F2}" name="xsk3g-no-hash" dataDxfId="85">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,K$2:K$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="11" xr3:uid="{CA3B62F6-6129-A24A-9549-B8B366058E32}" name="xsk4g-no-hash" dataDxfId="84">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,L$2:L$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="12" xr3:uid="{1A869223-8620-BD4F-9428-8E966A3DB61F}" name="2g-hash-at-both" dataDxfId="83">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,M$2:M$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="13" xr3:uid="{24A6594B-092E-3C4F-8A5F-47E5BB46BB2E}" name="3g-hash-at-both" dataDxfId="82">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,N$2:N$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="14" xr3:uid="{16D8FD4F-762F-2F43-867F-15E30B5AD39D}" name="4g-hash-at-both" dataDxfId="81">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,O$2:O$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="15" xr3:uid="{76D12C91-CCEF-C848-BB96-F03B2CD62923}" name="xsk2g-hash-at-both" dataDxfId="80">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,P$2:P$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="16" xr3:uid="{81B15818-6876-A44C-A260-2A604BAEBA82}" name="xsk3g-hash-at-both" dataDxfId="79">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,Q$2:Q$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="17" xr3:uid="{68EEFDA4-F174-D544-B865-C8873AAC456B}" name="xsk4g-hash-at-both" dataDxfId="78">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,R$2:R$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="18" xr3:uid="{305EE662-6124-4B43-A625-37C51A44D2EB}" name="max" dataDxfId="77">
-      <calculatedColumnFormula>_xlfn.LET(_xlpm.d,$G23:$R23,MAX(_xlpm.d))</calculatedColumnFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{C401E4AC-E1BD-4B46-BA1F-009F8AD77F50}" name="Table7" displayName="Table7" ref="B36:R42" totalsRowShown="0">
-  <autoFilter ref="B36:R42" xr:uid="{C401E4AC-E1BD-4B46-BA1F-009F8AD77F50}"/>
-  <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{56B3EF89-7FD5-B942-BB80-1168A5FD3080}" name="attribute.index"/>
-    <tableColumn id="2" xr3:uid="{B3B6F63C-9DCD-1145-9396-EEA93ED3F654}" name="attribute"/>
-    <tableColumn id="3" xr3:uid="{26C64D56-F266-964B-84C2-81CC0155F159}" name="supplemented"/>
-    <tableColumn id="4" xr3:uid="{3DD6726E-6154-7246-AD5A-A532BFD45820}" name="method.index"/>
-    <tableColumn id="5" xr3:uid="{9EE0ACFE-5BFA-C545-B5E1-8AC65D7DA907}" name="metric"/>
-    <tableColumn id="6" xr3:uid="{B25ED553-0048-354F-8E6A-9CA218DDA650}" name="2g-no-hash" dataDxfId="76">
-      <calculatedColumnFormula>_xlfn.LET(_xlpm.d,$G23:$X23,RANK(G23,_xlpm.d))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="7" xr3:uid="{43AF6FE3-AB63-2947-92C1-DFBC7EB0B01C}" name="3g-no-hash" dataDxfId="75">
-      <calculatedColumnFormula>_xlfn.LET(_xlpm.d,$G23:$X23,RANK(H23,_xlpm.d))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="8" xr3:uid="{68B4DDFF-FE87-1A4A-8AE5-2D25C1A0F149}" name="4g-no-hash" dataDxfId="74">
-      <calculatedColumnFormula>_xlfn.LET(_xlpm.d,$G23:$X23,RANK(I23,_xlpm.d))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="9" xr3:uid="{2660BFF4-80A4-BE42-ABDA-FD0CEC726255}" name="xsk2g-no-hash" dataDxfId="73">
-      <calculatedColumnFormula>_xlfn.LET(_xlpm.d,$G23:$X23,RANK(J23,_xlpm.d))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="10" xr3:uid="{EADBDB0B-2F23-484D-B529-BAB92E32C6CF}" name="xsk3g-no-hash" dataDxfId="72">
-      <calculatedColumnFormula>_xlfn.LET(_xlpm.d,$G23:$X23,RANK(K23,_xlpm.d))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="11" xr3:uid="{B5C4D9BB-9BB8-9C44-AEAB-770E9AA3A25C}" name="xsk4g-no-hash" dataDxfId="71">
-      <calculatedColumnFormula>_xlfn.LET(_xlpm.d,$G23:$X23,RANK(L23,_xlpm.d))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="12" xr3:uid="{DB7B33B1-2A72-E84E-BAD1-F7CAC688F8FE}" name="2g-hash-at-both" dataDxfId="70">
-      <calculatedColumnFormula>_xlfn.LET(_xlpm.d,$G23:$X23,RANK(M23,_xlpm.d))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="13" xr3:uid="{6A1E6416-EF0B-7743-B8BA-75D1227DD32C}" name="3g-hash-at-both" dataDxfId="69">
-      <calculatedColumnFormula>_xlfn.LET(_xlpm.d,$G23:$X23,RANK(N23,_xlpm.d))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="14" xr3:uid="{5E6B89E7-58A3-904C-9E47-0E3C51164BB7}" name="4g-hash-at-both" dataDxfId="68">
-      <calculatedColumnFormula>_xlfn.LET(_xlpm.d,$G23:$X23,RANK(O23,_xlpm.d))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="15" xr3:uid="{21219D4A-B484-A546-8EDD-17BC82C048DA}" name="xsk2g-hash-at-both" dataDxfId="67">
-      <calculatedColumnFormula>_xlfn.LET(_xlpm.d,$G23:$X23,RANK(P23,_xlpm.d))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="16" xr3:uid="{3F4A3F78-7141-834C-94FF-F2D1E1F5E38D}" name="xsk3g-hash-at-both" dataDxfId="66">
-      <calculatedColumnFormula>_xlfn.LET(_xlpm.d,$G23:$X23,RANK(Q23,_xlpm.d))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="17" xr3:uid="{7A5E4F7B-263F-8A4C-B443-A6716A44D562}" name="xsk4g-hash-at-both" dataDxfId="65">
-      <calculatedColumnFormula>_xlfn.LET(_xlpm.d,$G23:$X23,RANK(R23,_xlpm.d))</calculatedColumnFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{C8AA9E6E-9BDF-1C41-9893-B2A889CB478D}" name="Table110" displayName="Table110" ref="A1:S19" totalsRowShown="0">
-  <autoFilter ref="A1:S19" xr:uid="{62C33DBD-BDE4-1C46-98BA-06D036BEAD6C}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S19">
-    <sortCondition ref="B1:B19"/>
-  </sortState>
-  <tableColumns count="19">
-    <tableColumn id="1" xr3:uid="{612E2458-8E74-E246-967D-A1170869A747}" name="lang"/>
-    <tableColumn id="18" xr3:uid="{89A23AED-ED8C-9A49-8C70-5D1DEB97FE73}" name="attribute.index"/>
-    <tableColumn id="2" xr3:uid="{37C7A035-F8C8-5C4E-B4DF-D5CA0A5AA5C0}" name="attribute"/>
-    <tableColumn id="3" xr3:uid="{D031297D-F6F0-F945-A74D-A8BAE29FEE55}" name="supplement"/>
-    <tableColumn id="19" xr3:uid="{2A2BCDDA-0C60-DC40-AF52-00C0532F7B82}" name="method.index"/>
-    <tableColumn id="4" xr3:uid="{19FC2FCD-ECC9-D442-A745-B77EC4D15D13}" name="method"/>
-    <tableColumn id="5" xr3:uid="{61F795D1-9E55-AB44-89F2-30248F7E7921}" name="2g-no-hash" dataDxfId="64"/>
-    <tableColumn id="6" xr3:uid="{BA3712E0-7A40-E642-9775-AE6726A869D6}" name="3g-no-hash" dataDxfId="63"/>
-    <tableColumn id="7" xr3:uid="{3E362E7F-22CE-E54F-9E30-F0DD80594D23}" name="4g-no-hash" dataDxfId="62"/>
-    <tableColumn id="8" xr3:uid="{50A69ACA-7DD9-E64F-9494-40EBEAAAD1C4}" name="xsk2g-no-hash" dataDxfId="61"/>
-    <tableColumn id="9" xr3:uid="{1DE1AB3A-CCB6-3F44-B627-CABF64E6B6F6}" name="xsk3g-no-hash" dataDxfId="60"/>
-    <tableColumn id="10" xr3:uid="{6263A08D-944F-544F-8AEE-E306F3E4ACF4}" name="xsk4g-no-hash" dataDxfId="59"/>
-    <tableColumn id="11" xr3:uid="{3DA6AB8A-AD01-4845-B5BE-43566F03A32A}" name="2g-hash-at-both" dataDxfId="58"/>
-    <tableColumn id="12" xr3:uid="{04215951-6057-AD49-AB22-8B071068C09D}" name="3g-hash-at-both" dataDxfId="57"/>
-    <tableColumn id="13" xr3:uid="{7D4FDBA7-8A34-9D44-B243-20E6BC181153}" name="4g-hash-at-both" dataDxfId="56"/>
-    <tableColumn id="14" xr3:uid="{FE537402-E705-644F-A11E-E90E23B298C0}" name="xsk2g-hash-at-both" dataDxfId="55"/>
-    <tableColumn id="15" xr3:uid="{9C1F0C1D-19D8-8A46-92D0-540EE49FE079}" name="xsk3g-hash-at-both" dataDxfId="54"/>
-    <tableColumn id="16" xr3:uid="{5F8AA456-A2ED-E54A-9ACC-D43290DC1953}" name="xsk4g-hash-at-both" dataDxfId="53"/>
-    <tableColumn id="17" xr3:uid="{018C34F6-72C5-2547-9484-230A2CCDD554}" name="max" dataDxfId="52">
-      <calculatedColumnFormula>_xlfn.LET(_xlpm.d,$G2:$R2,MAX(_xlpm.d))</calculatedColumnFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{E6E828DD-BAE1-0D41-B9FF-3A80A0F38066}" name="Table11" displayName="Table11" ref="B22:S28" totalsRowShown="0" headerRowDxfId="51">
-  <autoFilter ref="B22:S28" xr:uid="{E6E828DD-BAE1-0D41-B9FF-3A80A0F38066}"/>
-  <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{06BBAFA8-30C7-C943-B7B1-4D009BACCC00}" name="attribute.index"/>
-    <tableColumn id="2" xr3:uid="{04BDCF93-74B8-CC4A-A151-23AC2D697B6F}" name="attribute"/>
-    <tableColumn id="3" xr3:uid="{3F09466F-54C9-334F-8E20-CCCABE1373DF}" name="supplemented"/>
-    <tableColumn id="4" xr3:uid="{E8A38307-6316-0041-B295-75A92A0187E6}" name="method.index"/>
-    <tableColumn id="5" xr3:uid="{28286CCA-7DD9-D94A-A25C-AB2EC960B357}" name="metric"/>
-    <tableColumn id="6" xr3:uid="{C942D0AF-F8A3-1043-984F-2D0BE85CFC51}" name="2g-no-hash" dataDxfId="50">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,G$2:G$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="7" xr3:uid="{46AAE389-CF33-4B4D-B11D-699824564800}" name="3g-no-hash" dataDxfId="49">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,H$2:H$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="8" xr3:uid="{C2427AF7-1AE5-5947-BB1C-45E6E7B9E7ED}" name="4g-no-hash" dataDxfId="48">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,I$2:I$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="9" xr3:uid="{ED956FEA-5A7D-4A45-915C-BCF1582E2B9D}" name="xsk2g-no-hash" dataDxfId="47">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,J$2:J$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="10" xr3:uid="{A7300332-F14F-DA4D-BD71-A77BDE7F01B2}" name="xsk3g-no-hash" dataDxfId="46">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,K$2:K$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="11" xr3:uid="{F73D60C9-BB5E-3D4E-94A3-85A2A6240EE4}" name="xsk4g-no-hash" dataDxfId="45">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,L$2:L$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="12" xr3:uid="{9D8FFDA0-8AC1-C44C-878E-9D27D35F7960}" name="2g-hash-at-both" dataDxfId="44">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,M$2:M$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="13" xr3:uid="{74B5B9B3-D509-8844-9208-5E11B511B031}" name="3g-hash-at-both" dataDxfId="43">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,N$2:N$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="14" xr3:uid="{9B9CBD0C-6763-7042-A123-E3282BC788CB}" name="4g-hash-at-both" dataDxfId="42">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,O$2:O$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="15" xr3:uid="{BCA72DE9-CE40-BA4D-80A7-D3D2D6BC2FA4}" name="xsk2g-hash-at-both" dataDxfId="41">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,P$2:P$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="16" xr3:uid="{48136231-ABB5-C84B-A976-63BF06D63B16}" name="xsk3g-hash-at-both" dataDxfId="40">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,Q$2:Q$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="17" xr3:uid="{4564DDDC-A2E5-E648-ADD7-2806FEF7A95B}" name="xsk4g-hash-at-both" dataDxfId="39">
-      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,R$2:R$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="18" xr3:uid="{EF6262A8-36CD-B94D-84E3-31FF184250FF}" name="max" dataDxfId="38">
-      <calculatedColumnFormula>_xlfn.LET(_xlpm.d,$G23:$R23,MAX(_xlpm.d))</calculatedColumnFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{20CFC09F-4CA7-5A4B-8710-2254971E0D64}" name="Table3" displayName="Table3" ref="A1:S19" totalsRowShown="0">
-  <autoFilter ref="A1:S19" xr:uid="{20CFC09F-4CA7-5A4B-8710-2254971E0D64}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S19">
-    <sortCondition ref="B1:B19"/>
-  </sortState>
-  <tableColumns count="19">
-    <tableColumn id="1" xr3:uid="{BF35C7E1-BA33-8348-81F9-C57324460597}" name="lang"/>
-    <tableColumn id="2" xr3:uid="{D5E39B1A-2425-1D4E-BC5B-18BE3E7E6660}" name="attribute.index"/>
-    <tableColumn id="3" xr3:uid="{6BAA365A-F6C8-5D4C-8F01-4A53503BDC88}" name="attribute"/>
-    <tableColumn id="4" xr3:uid="{584BAD1A-9B8E-0547-96D9-A92A5A8DE50C}" name="supplement"/>
-    <tableColumn id="5" xr3:uid="{9A00C24F-08E3-E844-B5A6-E2D6D4403A02}" name="method.index"/>
-    <tableColumn id="6" xr3:uid="{FAC137F9-992F-F84A-8FEB-6E306FB9B6B7}" name="method"/>
-    <tableColumn id="7" xr3:uid="{B0EA0C28-58A7-7847-A0A3-D5CED943EFC0}" name="2g-no-hash" dataDxfId="37"/>
-    <tableColumn id="8" xr3:uid="{EA3E43C7-1764-C347-A3E2-7D20096614E3}" name="3g-no-hash" dataDxfId="36"/>
-    <tableColumn id="9" xr3:uid="{908B93EF-68ED-B840-9D06-53E9DA28FADB}" name="4g-no-hash" dataDxfId="35"/>
-    <tableColumn id="10" xr3:uid="{A5CA07AC-2A66-C543-B13E-DD6CE094F3E3}" name="xsk2g-no-hash" dataDxfId="34"/>
-    <tableColumn id="11" xr3:uid="{26A5F9ED-F6B2-134F-B1DC-AC26E155B105}" name="xsk3g-no-hash" dataDxfId="33"/>
-    <tableColumn id="12" xr3:uid="{F47EE545-5E10-4848-BD75-A72E0AFE04AB}" name="xsk4g-no-hash" dataDxfId="32"/>
-    <tableColumn id="13" xr3:uid="{AE7DBC1B-0B86-6844-A15A-A2602343D372}" name="2g-hash-at-both" dataDxfId="31"/>
-    <tableColumn id="14" xr3:uid="{465F812F-73F8-8548-9144-04C25B3C278A}" name="3g-hash-at-both" dataDxfId="30"/>
-    <tableColumn id="15" xr3:uid="{71E8F9E2-32E5-CC4E-A9B4-9BEB76A59277}" name="4g-hash-at-both" dataDxfId="29"/>
-    <tableColumn id="16" xr3:uid="{8AD668A4-7E49-9443-ABE3-AA6A4B0AE83D}" name="xsk2g-hash-at-both" dataDxfId="28"/>
-    <tableColumn id="17" xr3:uid="{861BBDFD-B295-FF44-9C9A-F8A1E16A6DDC}" name="xsk3g-hash-at-both" dataDxfId="27"/>
-    <tableColumn id="18" xr3:uid="{1A3A42F7-BD1E-504A-B956-CBC1CB0D9385}" name="xsk4g-hash-at-both" dataDxfId="26"/>
-    <tableColumn id="19" xr3:uid="{48EA1203-65AC-F84A-9C85-DD4C4DAE1843}" name="max" dataDxfId="25">
-      <calculatedColumnFormula>_xlfn.LET(_xlpm.d,$G2:$R2,MAX(_xlpm.d))</calculatedColumnFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{87F24483-B63C-3942-A489-0606D6A9489E}" name="Table2" displayName="Table2" ref="B22:S28" totalsRowShown="0">
   <autoFilter ref="B22:S28" xr:uid="{87F24483-B63C-3942-A489-0606D6A9489E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B23:S28">
@@ -10975,7 +5962,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{8D5B3FCA-ED32-0648-A329-5C488231AFA9}" name="Table4" displayName="Table4" ref="B36:R42" totalsRowShown="0">
   <autoFilter ref="B36:R42" xr:uid="{8D5B3FCA-ED32-0648-A329-5C488231AFA9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B37:R42">
@@ -11029,234 +6016,6 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{765B964F-59A4-6548-AEF0-4C279645DA85}" name="Table17" displayName="Table17" ref="A1:V5" totalsRowShown="0" headerRowDxfId="178" dataDxfId="177" tableBorderDxfId="176">
-  <autoFilter ref="A1:V5" xr:uid="{765B964F-59A4-6548-AEF0-4C279645DA85}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U5">
-    <sortCondition ref="G1:G5"/>
-  </sortState>
-  <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{CAD94501-C73B-B646-A615-AE7A2249D099}" name="lang" dataDxfId="175"/>
-    <tableColumn id="2" xr3:uid="{79289752-9986-7F44-B6CD-BE005D676309}" name="attribute.index" dataDxfId="174"/>
-    <tableColumn id="3" xr3:uid="{47082B48-EB41-BC40-94EA-809902A6AE4A}" name="attribute" dataDxfId="173"/>
-    <tableColumn id="4" xr3:uid="{9D401F41-41BC-E14F-954E-9D0BD3F583D0}" name="supplement" dataDxfId="172"/>
-    <tableColumn id="5" xr3:uid="{9B9341C7-60FF-FB4E-BA26-DB10530B0A92}" name="method.index" dataDxfId="171"/>
-    <tableColumn id="6" xr3:uid="{FDBCEE2A-B1DD-1347-95C7-FD49E9FF174D}" name="method" dataDxfId="170"/>
-    <tableColumn id="7" xr3:uid="{18A24558-BCE8-CE43-BB95-44E091D95F03}" name="ml" dataDxfId="169"/>
-    <tableColumn id="8" xr3:uid="{E366786D-7BA6-A441-8EC2-E37D2FA495C8}" name="sample" dataDxfId="168"/>
-    <tableColumn id="21" xr3:uid="{FBAA4B4B-19E8-D740-A464-DE7180D0C524}" name="var" dataDxfId="167">
-      <calculatedColumnFormula>_xlfn.TEXTJOIN({"","-","k-","-","-suppl:","-"},TRUE,"ml",G2,H2,A2,C2,D2)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="9" xr3:uid="{21D8E26F-7FF5-814D-A1AD-141726F764CC}" name="2g-no-hash" dataDxfId="166"/>
-    <tableColumn id="10" xr3:uid="{C6B705C8-EF2A-1F4B-A120-71E779DEE394}" name="3g-no-hash" dataDxfId="165"/>
-    <tableColumn id="11" xr3:uid="{CB5F23F3-D3EA-1E43-91CB-25FEE3195111}" name="4g-no-hash" dataDxfId="164"/>
-    <tableColumn id="12" xr3:uid="{241965AE-2238-8D46-9C47-13C4B48FD4D4}" name="xsk2g-no-hash" dataDxfId="163"/>
-    <tableColumn id="13" xr3:uid="{87B0510A-BDC3-6041-8ACB-991A222B5A8C}" name="xsk3g-no-hash" dataDxfId="162"/>
-    <tableColumn id="14" xr3:uid="{A31C6E12-6617-B748-88C2-CB35DC889076}" name="xsk4g-no-hash" dataDxfId="161"/>
-    <tableColumn id="15" xr3:uid="{8D393564-74FC-7642-9189-E29211AD6498}" name="2g-hash-at-both" dataDxfId="160"/>
-    <tableColumn id="16" xr3:uid="{44A9D067-E470-0649-B63E-668802B9E45D}" name="3g-hash-at-both" dataDxfId="159"/>
-    <tableColumn id="17" xr3:uid="{22AE43F7-61D8-E141-ACB4-ED227A475BF3}" name="4g-hash-at-both" dataDxfId="158"/>
-    <tableColumn id="18" xr3:uid="{EBE63269-CA77-494B-833A-91FD610AC993}" name="xsk2g-hash-at-both" dataDxfId="157"/>
-    <tableColumn id="19" xr3:uid="{28ED86B3-04B4-8F40-A953-4CF3B87012DC}" name="xsk3g-hash-at-both" dataDxfId="156"/>
-    <tableColumn id="20" xr3:uid="{794B7DFB-C5EB-4245-97F4-3878B9E16059}" name="xsk4g-hash-at-both" dataDxfId="155"/>
-    <tableColumn id="22" xr3:uid="{CF9D9C88-64E6-EF40-B4FF-2CE3DA0D6D8D}" name="max" dataDxfId="154">
-      <calculatedColumnFormula>_xlfn.LET(_xlpm.d,J2:T2,MAX(_xlpm.d))</calculatedColumnFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{A310F3C2-8B87-6144-A2FD-73529893744D}" name="Table18" displayName="Table18" ref="A8:V12" totalsRowShown="0" headerRowDxfId="153" tableBorderDxfId="152">
-  <autoFilter ref="A8:V12" xr:uid="{A310F3C2-8B87-6144-A2FD-73529893744D}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A9:U12">
-    <sortCondition descending="1" ref="H8:H12"/>
-  </sortState>
-  <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{ABD05C4C-C23E-7040-8B54-3062B86679C0}" name="lang"/>
-    <tableColumn id="2" xr3:uid="{5D05C351-B9EE-1845-A055-5491F15C6B9B}" name="attribute.index"/>
-    <tableColumn id="3" xr3:uid="{9E0FF1F6-5F20-C04E-8D19-381DABD42315}" name="attribute"/>
-    <tableColumn id="4" xr3:uid="{08B3D3CA-172C-084C-BD7F-278838B43FAE}" name="supplement"/>
-    <tableColumn id="5" xr3:uid="{539CB476-17F2-0246-8E5D-6373601CE134}" name="method.index"/>
-    <tableColumn id="6" xr3:uid="{5CA18A5F-A358-7D40-ABCB-5114437CA68F}" name="method"/>
-    <tableColumn id="7" xr3:uid="{7E1FBC6A-D77D-F440-AA90-D895FB2940A3}" name="ml" dataDxfId="151"/>
-    <tableColumn id="8" xr3:uid="{296F6D0E-3252-F249-9680-1C8B168DA8B5}" name="sample"/>
-    <tableColumn id="21" xr3:uid="{02E8055C-86A4-4D42-99CA-BBC6AF8BFF25}" name="var" dataDxfId="150">
-      <calculatedColumnFormula>_xlfn.TEXTJOIN({"","-","k-","-","-suppl:","-"},TRUE,"ml",G9,H9,A9,C9,D9)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="9" xr3:uid="{6D606557-4281-A24C-9BC2-8A0C49D30663}" name="2g-no-hash"/>
-    <tableColumn id="10" xr3:uid="{5DFE250F-AF9E-D74F-ACDC-34EAD601A5CC}" name="3g-no-hash"/>
-    <tableColumn id="11" xr3:uid="{3CC70F7D-A10A-9044-9B13-D3A6660DDF5E}" name="4g-no-hash"/>
-    <tableColumn id="12" xr3:uid="{B241AC89-271F-8247-9AF6-E388E5779DCA}" name="xsk2g-no-hash"/>
-    <tableColumn id="13" xr3:uid="{C7E4DDD0-52F7-034B-BB07-552777B4B339}" name="xsk3g-no-hash"/>
-    <tableColumn id="14" xr3:uid="{23DF3CAE-8E4D-2E47-9E93-33F20BEFAF75}" name="xsk4g-no-hash"/>
-    <tableColumn id="15" xr3:uid="{05251815-FCF4-9747-BA9B-D8FDB3B86281}" name="2g-hash-at-both"/>
-    <tableColumn id="16" xr3:uid="{A6EFDE52-285B-2E4B-BA16-B2E48BFE27D0}" name="3g-hash-at-both"/>
-    <tableColumn id="17" xr3:uid="{E4D67032-19CF-3F4F-AA05-8ABEBE2C1B3A}" name="4g-hash-at-both"/>
-    <tableColumn id="18" xr3:uid="{9E85EB0B-0695-EB40-9F75-5D6F9097A766}" name="xsk2g-hash-at-both"/>
-    <tableColumn id="19" xr3:uid="{3ECEE02C-BA1D-F14E-9CB2-13E5B9BE4B18}" name="xsk3g-hash-at-both"/>
-    <tableColumn id="20" xr3:uid="{B7D1E200-D876-AB44-AA71-BE9250C349F0}" name="xsk4g-hash-at-both"/>
-    <tableColumn id="22" xr3:uid="{F8E788BC-1B1F-D041-872C-6D04719075AB}" name="max" dataDxfId="149">
-      <calculatedColumnFormula>_xlfn.LET(_xlpm.d,J9:T9,MAX(_xlpm.d))</calculatedColumnFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{0AC66A05-4013-EF46-946C-B6EFA90E00F1}" name="Table19" displayName="Table19" ref="A15:V19" totalsRowShown="0" headerRowDxfId="148" tableBorderDxfId="147">
-  <autoFilter ref="A15:V19" xr:uid="{0AC66A05-4013-EF46-946C-B6EFA90E00F1}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A16:U19">
-    <sortCondition ref="G15:G19"/>
-  </sortState>
-  <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{6D72FD0D-D7C0-D54C-AD86-FC46EBD59DBA}" name="lang"/>
-    <tableColumn id="2" xr3:uid="{4AAF513E-4E5A-A047-8ADC-CBE3B15197B3}" name="attribute.index"/>
-    <tableColumn id="3" xr3:uid="{30B7DB44-3366-2A4A-B34B-3D186DE032A5}" name="attribute"/>
-    <tableColumn id="4" xr3:uid="{E7C376EC-BB02-BA4D-BCA8-2BEAB32668DA}" name="supplement"/>
-    <tableColumn id="5" xr3:uid="{0E09DA68-EEF9-2C41-9632-148FFC5E804B}" name="method.index"/>
-    <tableColumn id="6" xr3:uid="{B625C1A3-30B0-614E-91DE-A8CBF0447CFC}" name="method"/>
-    <tableColumn id="7" xr3:uid="{F3267743-81B1-394B-8C6A-52830009235F}" name="ml" dataDxfId="146"/>
-    <tableColumn id="8" xr3:uid="{8BC06710-2857-9B49-84F3-5BFFC487EC28}" name="sample"/>
-    <tableColumn id="21" xr3:uid="{7D975639-13C0-C442-9B13-2F0A67FCB11E}" name="var" dataDxfId="145">
-      <calculatedColumnFormula>_xlfn.TEXTJOIN({"","-","k-","-","-suppl:","-"},TRUE,"ml",G16,H16,A16,C16,D16)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="9" xr3:uid="{5D760736-AA21-004B-8D39-5BDF65E2CE3E}" name="2g-no-hash"/>
-    <tableColumn id="10" xr3:uid="{6C202BCA-686E-6E4D-A7B5-D115203C2B69}" name="3g-no-hash"/>
-    <tableColumn id="11" xr3:uid="{E26BA085-6897-A44A-941F-06AD94EC803F}" name="4g-no-hash"/>
-    <tableColumn id="12" xr3:uid="{1CEAE802-9908-C343-B9FD-CA27BBF2F69A}" name="xsk2g-no-hash"/>
-    <tableColumn id="13" xr3:uid="{576CA549-C779-FF4A-9B54-F4635929B462}" name="xsk3g-no-hash"/>
-    <tableColumn id="14" xr3:uid="{3B5A5BD2-8A4F-814F-9B58-54B8169A20C8}" name="xsk4g-no-hash"/>
-    <tableColumn id="15" xr3:uid="{B623AEDD-7094-C34A-B24B-4D4E9D4203D7}" name="2g-hash-at-both"/>
-    <tableColumn id="16" xr3:uid="{65CD250F-2A4B-BA43-B46F-AA2EC8C4C714}" name="3g-hash-at-both"/>
-    <tableColumn id="17" xr3:uid="{9C230E61-28E7-FC40-984E-610F4568A38A}" name="4g-hash-at-both"/>
-    <tableColumn id="18" xr3:uid="{19DF6E6A-0DD6-7143-BB7D-FB0BFD7EB9BD}" name="xsk2g-hash-at-both"/>
-    <tableColumn id="19" xr3:uid="{734554F5-D95A-394D-BBEE-92E3C49E54AB}" name="xsk3g-hash-at-both"/>
-    <tableColumn id="20" xr3:uid="{32E10DD0-6930-5645-9089-B7E607EB05E7}" name="xsk4g-hash-at-both"/>
-    <tableColumn id="22" xr3:uid="{E7E73336-72C0-5C47-B8C9-50A3A0142E1F}" name="max" dataDxfId="144">
-      <calculatedColumnFormula>_xlfn.LET(_xlpm.d,J16:T16,MAX(_xlpm.d))</calculatedColumnFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{11A43BE0-DE44-424F-A996-1F757A670B1A}" name="Table20" displayName="Table20" ref="A22:V26" totalsRowShown="0" headerRowDxfId="143" tableBorderDxfId="142">
-  <autoFilter ref="A22:V26" xr:uid="{11A43BE0-DE44-424F-A996-1F757A670B1A}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A23:U26">
-    <sortCondition ref="G22:G26"/>
-  </sortState>
-  <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{1253FC50-8183-CE4D-AE42-FD2C9476BE41}" name="lang"/>
-    <tableColumn id="2" xr3:uid="{5140B78F-F5C5-9549-A03B-D86BB0F72F26}" name="attribute.index"/>
-    <tableColumn id="3" xr3:uid="{97B68EEE-EAAC-2649-AB31-0B0CC7ABA432}" name="attribute"/>
-    <tableColumn id="4" xr3:uid="{68ADCC08-BA06-7B4C-88A5-AD15B6461480}" name="supplement"/>
-    <tableColumn id="5" xr3:uid="{FC0F4BBC-4840-9043-908F-51077519D310}" name="method.index"/>
-    <tableColumn id="6" xr3:uid="{212E16CE-3D07-F44E-86B0-811CE990D31D}" name="method"/>
-    <tableColumn id="7" xr3:uid="{BFC4A0A1-5D87-F547-AF0A-AB020EF326B6}" name="ml" dataDxfId="141"/>
-    <tableColumn id="8" xr3:uid="{76DACB40-FA88-4A47-80DA-E8C30292D444}" name="sample"/>
-    <tableColumn id="21" xr3:uid="{25FE4B79-2DB7-0A46-8545-1B48DAA37EC0}" name="var" dataDxfId="140">
-      <calculatedColumnFormula>_xlfn.TEXTJOIN({"","-","k-","-","-suppl:","-"},TRUE,"ml",G23,H23,A23,C23,D23)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="9" xr3:uid="{EB79C7CD-F6AB-A240-9217-18BB6E4A84ED}" name="2g-no-hash"/>
-    <tableColumn id="10" xr3:uid="{3C3D2F4D-261F-9940-889F-DA7915075E27}" name="3g-no-hash"/>
-    <tableColumn id="11" xr3:uid="{677F02DC-3433-9A41-BBC4-9E6014057672}" name="4g-no-hash"/>
-    <tableColumn id="12" xr3:uid="{8F7EE5F7-DAB7-8D4B-9B05-5C651937897E}" name="xsk2g-no-hash"/>
-    <tableColumn id="13" xr3:uid="{25217851-680A-224D-B48D-6786F399481F}" name="xsk3g-no-hash"/>
-    <tableColumn id="14" xr3:uid="{ECC57184-8BD3-9242-98C4-C7027CCCD964}" name="xsk4g-no-hash"/>
-    <tableColumn id="15" xr3:uid="{824F0E21-6CFD-634F-9581-B9FEA4BC0D83}" name="2g-hash-at-both"/>
-    <tableColumn id="16" xr3:uid="{DF3A895E-96F1-484F-8B4E-CBFD39578634}" name="3g-hash-at-both"/>
-    <tableColumn id="17" xr3:uid="{D1030C9C-EB6A-8C40-9555-E0C018DAC5EE}" name="4g-hash-at-both"/>
-    <tableColumn id="18" xr3:uid="{09C23254-8601-EC46-B352-0E009C9D6562}" name="xsk2g-hash-at-both"/>
-    <tableColumn id="19" xr3:uid="{FE6B2A18-B682-CF40-8C4D-D95DBE21F6F7}" name="xsk3g-hash-at-both"/>
-    <tableColumn id="20" xr3:uid="{07FB3FFB-6337-B640-BB91-6583F7E9FE79}" name="xsk4g-hash-at-both"/>
-    <tableColumn id="22" xr3:uid="{5DEB2C6D-6D62-B54E-87A5-4E098791A429}" name="max" dataDxfId="139">
-      <calculatedColumnFormula>_xlfn.LET(_xlpm.d,J23:T23,MAX(_xlpm.d))</calculatedColumnFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{71B92A3A-DAC9-0B47-BB0D-C131D27B59AC}" name="Table21" displayName="Table21" ref="A29:V33" totalsRowShown="0" headerRowDxfId="138" tableBorderDxfId="137">
-  <autoFilter ref="A29:V33" xr:uid="{71B92A3A-DAC9-0B47-BB0D-C131D27B59AC}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A30:U33">
-    <sortCondition ref="G29:G33"/>
-  </sortState>
-  <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{CFB1DB43-B35C-4747-946D-E2D90E18698A}" name="lang"/>
-    <tableColumn id="2" xr3:uid="{75AD2146-BC02-9542-A9E4-C62B02DA710D}" name="attribute.index"/>
-    <tableColumn id="3" xr3:uid="{4F587539-6AAA-CA4F-B146-335FF2277696}" name="attribute"/>
-    <tableColumn id="4" xr3:uid="{774BCCB1-8685-C846-A1AE-A3E33563C9DB}" name="supplement"/>
-    <tableColumn id="5" xr3:uid="{DB462237-3E05-3047-878A-628CE4B6C765}" name="method.index"/>
-    <tableColumn id="6" xr3:uid="{BDDDC413-4D60-374B-9A34-323C5C6F6700}" name="method"/>
-    <tableColumn id="7" xr3:uid="{70037FEF-6ECE-B443-BCC2-3C7BFB733425}" name="ml" dataDxfId="136"/>
-    <tableColumn id="8" xr3:uid="{6B5C538D-EC74-024D-B036-677D8C05EE47}" name="sample"/>
-    <tableColumn id="21" xr3:uid="{34832294-86A8-104B-8E94-4A75EFFDD352}" name="var" dataDxfId="135">
-      <calculatedColumnFormula>_xlfn.TEXTJOIN({"","-","k-","-","-suppl:","-"},TRUE,"ml",G30,H30,A30,C30,D30)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="9" xr3:uid="{287DD20C-74ED-0442-8E1B-175ADCD625EE}" name="2g-no-hash"/>
-    <tableColumn id="10" xr3:uid="{048CA4C3-F221-704E-9CC0-895CB92E3727}" name="3g-no-hash"/>
-    <tableColumn id="11" xr3:uid="{AFA9C4C3-5B68-274D-850C-AFAF445E744B}" name="4g-no-hash"/>
-    <tableColumn id="12" xr3:uid="{00136F3E-9E91-B94C-8637-2C06CDCB399A}" name="xsk2g-no-hash"/>
-    <tableColumn id="13" xr3:uid="{F85DC81C-F69D-F84F-8E44-18B45D85F785}" name="xsk3g-no-hash"/>
-    <tableColumn id="14" xr3:uid="{368D05A2-2655-DE49-8ACC-BCAC890EDDFD}" name="xsk4g-no-hash"/>
-    <tableColumn id="15" xr3:uid="{CFD672EA-BFC2-7544-8F43-E1B93B36A189}" name="2g-hash-at-both"/>
-    <tableColumn id="16" xr3:uid="{0409C177-638E-8C42-ABF9-F5363D4DD2F5}" name="3g-hash-at-both"/>
-    <tableColumn id="17" xr3:uid="{091A9CFC-7607-D248-A1D2-503D14FF7949}" name="4g-hash-at-both"/>
-    <tableColumn id="18" xr3:uid="{B014E544-4CC7-BA4B-8A32-F82BE4BFA27C}" name="xsk2g-hash-at-both"/>
-    <tableColumn id="19" xr3:uid="{E5166787-6956-3E47-A171-3BB760A87635}" name="xsk3g-hash-at-both"/>
-    <tableColumn id="20" xr3:uid="{B842EF27-B3D8-324D-95BC-F466F3678301}" name="xsk4g-hash-at-both"/>
-    <tableColumn id="22" xr3:uid="{673077EE-FE89-C844-BD7D-675C4A266AB7}" name="max" dataDxfId="134">
-      <calculatedColumnFormula>_xlfn.LET(_xlpm.d,J30:T30,MAX(_xlpm.d))</calculatedColumnFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{897541B0-F457-FF43-9DAB-006B7A7E30D1}" name="Table22" displayName="Table22" ref="A36:V40" totalsRowShown="0" headerRowDxfId="133" tableBorderDxfId="132">
-  <autoFilter ref="A36:V40" xr:uid="{897541B0-F457-FF43-9DAB-006B7A7E30D1}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A37:U40">
-    <sortCondition ref="G36:G40"/>
-  </sortState>
-  <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{DA54905B-F877-134B-9007-1BE1C2F7DDA5}" name="lang"/>
-    <tableColumn id="2" xr3:uid="{2CB3CD3F-A66A-2944-A753-30474A034E12}" name="attribute.index"/>
-    <tableColumn id="3" xr3:uid="{43705036-AE85-9B49-8075-FE1FF6DC9B83}" name="attribute"/>
-    <tableColumn id="4" xr3:uid="{9735BCDE-11FF-F048-89F8-57D01F368174}" name="supplement"/>
-    <tableColumn id="5" xr3:uid="{924F77F5-46B9-7148-AF5F-BA902F69174F}" name="method.index"/>
-    <tableColumn id="6" xr3:uid="{897D1E18-0A39-BA40-8D31-F484184348DC}" name="method"/>
-    <tableColumn id="7" xr3:uid="{26CA8DB5-EE25-4B40-A44A-4B3DBC68C5F5}" name="ml" dataDxfId="131"/>
-    <tableColumn id="8" xr3:uid="{2B6A9916-68AB-8E45-BDC3-F663180FA2FD}" name="sample"/>
-    <tableColumn id="21" xr3:uid="{7DB45073-D754-904E-BEA9-FBB95C933A43}" name="var" dataDxfId="130">
-      <calculatedColumnFormula>_xlfn.TEXTJOIN({"","-","k-","-","-suppl:","-"},TRUE,"ml",G37,H37,A37,C37,D37)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="9" xr3:uid="{2245193E-C133-7E42-BC82-8FD8AF20BE31}" name="2g-no-hash"/>
-    <tableColumn id="10" xr3:uid="{D528C58D-142C-7B4B-BC09-1F0B1E777E7D}" name="3g-no-hash"/>
-    <tableColumn id="11" xr3:uid="{FF0BB617-DDC2-F84D-8F30-5AB93367956F}" name="4g-no-hash"/>
-    <tableColumn id="12" xr3:uid="{A115A404-CF39-6444-A93E-090368E25BD7}" name="xsk2g-no-hash"/>
-    <tableColumn id="13" xr3:uid="{00300682-428E-4C4B-95C5-21BA23575C29}" name="xsk3g-no-hash"/>
-    <tableColumn id="14" xr3:uid="{BAEEC922-C532-8C44-BB78-8F0514936A75}" name="xsk4g-no-hash"/>
-    <tableColumn id="15" xr3:uid="{F79B776B-3634-7C46-8F64-67DB1B0F9ED0}" name="2g-hash-at-both"/>
-    <tableColumn id="16" xr3:uid="{867A2FBF-48C6-7A40-AD9E-EFC2F4F6C56D}" name="3g-hash-at-both"/>
-    <tableColumn id="17" xr3:uid="{AD40F758-4B9B-4F4A-A993-0D0217939326}" name="4g-hash-at-both"/>
-    <tableColumn id="18" xr3:uid="{A5F15E5D-D559-BB41-A7D1-0FD826E00D38}" name="xsk2g-hash-at-both"/>
-    <tableColumn id="19" xr3:uid="{A92101F6-260C-4E43-937D-D6C4E762C20E}" name="xsk3g-hash-at-both"/>
-    <tableColumn id="20" xr3:uid="{8139A429-C3A5-004A-A823-BA1BE31F4E0D}" name="xsk4g-hash-at-both"/>
-    <tableColumn id="23" xr3:uid="{64EE52A0-D8CB-BE4A-A27C-8BA83546D415}" name="max" dataDxfId="129">
-      <calculatedColumnFormula>_xlfn.LET(_xlpm.d,J37:T37,MAX(_xlpm.d))</calculatedColumnFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{616F4647-0403-454A-9D15-AA0FF8411E8C}" name="Table12" displayName="Table12" ref="A1:S19" totalsRowShown="0">
   <autoFilter ref="A1:S19" xr:uid="{616F4647-0403-454A-9D15-AA0FF8411E8C}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S19">
@@ -11289,7 +6048,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{37D28673-FEE1-7644-AF9B-5CF63EA2E264}" name="Table13" displayName="Table13" ref="B22:S28" totalsRowShown="0">
   <autoFilter ref="B22:S28" xr:uid="{37D28673-FEE1-7644-AF9B-5CF63EA2E264}"/>
   <tableColumns count="18">
@@ -11336,6 +6095,261 @@
     </tableColumn>
     <tableColumn id="18" xr3:uid="{C4BBBE98-6ACE-DC4E-B169-0F7742CE5BD5}" name="max" dataDxfId="103">
       <calculatedColumnFormula>_xlfn.LET(_xlpm.d,$G23:$R23,MAX(_xlpm.d))</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AECC5072-F047-8B44-8BB6-96052FE91454}" name="Table1" displayName="Table1" ref="A1:S19" totalsRowShown="0">
+  <autoFilter ref="A1:S19" xr:uid="{AECC5072-F047-8B44-8BB6-96052FE91454}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S19">
+    <sortCondition ref="B1:B19"/>
+  </sortState>
+  <tableColumns count="19">
+    <tableColumn id="1" xr3:uid="{1327DC5E-DC70-8A4D-9B1F-3995AE90E6FD}" name="lang"/>
+    <tableColumn id="2" xr3:uid="{5EF94ABC-9242-3F46-B0A6-BF578616549F}" name="attribute.index"/>
+    <tableColumn id="3" xr3:uid="{7ABA1446-5876-F742-BFE2-C40E3818548C}" name="attribute"/>
+    <tableColumn id="4" xr3:uid="{57C4556B-D00C-D24E-BADF-6D97D0CA4318}" name="supplement"/>
+    <tableColumn id="5" xr3:uid="{988388D8-7223-204B-885D-63BE8FD231BA}" name="method.index"/>
+    <tableColumn id="6" xr3:uid="{B6E039AA-5879-304A-BF97-3FD1C15339DC}" name="method"/>
+    <tableColumn id="7" xr3:uid="{B547C5B4-5DE8-A540-9F99-C08EB5487E2F}" name="2g-no-hash" dataDxfId="102"/>
+    <tableColumn id="8" xr3:uid="{61EE02A8-7C51-254F-8C4A-F987370F31B4}" name="3g-no-hash" dataDxfId="101"/>
+    <tableColumn id="9" xr3:uid="{F7CEC792-9442-5845-B7FA-B7EB0C6BAFDB}" name="4g-no-hash" dataDxfId="100"/>
+    <tableColumn id="10" xr3:uid="{48A3ABF5-42C0-B247-966C-F76FC9295319}" name="xsk2g-no-hash" dataDxfId="99"/>
+    <tableColumn id="11" xr3:uid="{75523B27-FF4E-9041-B642-195593D373FD}" name="xsk3g-no-hash" dataDxfId="98"/>
+    <tableColumn id="12" xr3:uid="{CE927920-C222-0044-863A-CD6CCEAB0264}" name="xsk4g-no-hash" dataDxfId="97"/>
+    <tableColumn id="13" xr3:uid="{5355CE3B-D063-B74D-B6EE-829545E87A85}" name="2g-hash-at-both" dataDxfId="96"/>
+    <tableColumn id="14" xr3:uid="{5A4024C9-DD8A-344F-A354-E76F042BB0C4}" name="3g-hash-at-both" dataDxfId="95"/>
+    <tableColumn id="15" xr3:uid="{D0F84E10-490E-FC49-B941-5607004585D3}" name="4g-hash-at-both" dataDxfId="94"/>
+    <tableColumn id="16" xr3:uid="{0BC3C2D0-5994-B046-991C-31524C3441D2}" name="xsk2g-hash-at-both" dataDxfId="93"/>
+    <tableColumn id="17" xr3:uid="{3A798061-F077-CA49-859C-963FFBF75831}" name="xsk3g-hash-at-both" dataDxfId="92"/>
+    <tableColumn id="18" xr3:uid="{36B31AED-5A21-3849-9CEF-A3C4A9D16F62}" name="xsk4g-hash-at-both" dataDxfId="91"/>
+    <tableColumn id="19" xr3:uid="{D46E6BD6-2DB9-F94B-BE12-5609179FA557}" name="max" dataDxfId="90">
+      <calculatedColumnFormula>_xlfn.LET(_xlpm.d,$G2:$R2,MAX(_xlpm.d))</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{0692717F-4AD9-5A43-997B-DECCE73C02C3}" name="Table5" displayName="Table5" ref="B22:S28" totalsRowShown="0">
+  <autoFilter ref="B22:S28" xr:uid="{0692717F-4AD9-5A43-997B-DECCE73C02C3}"/>
+  <tableColumns count="18">
+    <tableColumn id="1" xr3:uid="{0A4D604F-F8C1-0B4B-90C6-EAE050C704E4}" name="attribute.index"/>
+    <tableColumn id="2" xr3:uid="{9D57305A-6224-C542-96F4-FBD9797D0BF6}" name="attribute"/>
+    <tableColumn id="3" xr3:uid="{ABC18CB5-FED7-464B-993D-7CA8FB4F071A}" name="supplemented"/>
+    <tableColumn id="4" xr3:uid="{847EC6B0-B5D5-F247-A98B-9ED19BC48F2A}" name="method.index"/>
+    <tableColumn id="5" xr3:uid="{0ECBE385-F3F8-C340-8178-A4CB9B4B23B7}" name="metric"/>
+    <tableColumn id="6" xr3:uid="{15590882-F724-4343-85D1-377170A0E8EE}" name="2g-no-hash" dataDxfId="89">
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,G$2:G$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{A52E75AE-F946-5447-8299-5982E85CF780}" name="3g-no-hash" dataDxfId="88">
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,H$2:H$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{CDC64800-2690-CF48-BD74-EC01BE5C66DC}" name="4g-no-hash" dataDxfId="87">
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,I$2:I$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{82E7043E-D5FC-8F41-AA0B-8E3099E7D351}" name="xsk2g-no-hash" dataDxfId="86">
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,J$2:J$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{DCA1203B-8423-0744-8464-5312746CD7F2}" name="xsk3g-no-hash" dataDxfId="85">
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,K$2:K$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="11" xr3:uid="{CA3B62F6-6129-A24A-9549-B8B366058E32}" name="xsk4g-no-hash" dataDxfId="84">
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,L$2:L$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="12" xr3:uid="{1A869223-8620-BD4F-9428-8E966A3DB61F}" name="2g-hash-at-both" dataDxfId="83">
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,M$2:M$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="13" xr3:uid="{24A6594B-092E-3C4F-8A5F-47E5BB46BB2E}" name="3g-hash-at-both" dataDxfId="82">
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,N$2:N$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="14" xr3:uid="{16D8FD4F-762F-2F43-867F-15E30B5AD39D}" name="4g-hash-at-both" dataDxfId="81">
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,O$2:O$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="15" xr3:uid="{76D12C91-CCEF-C848-BB96-F03B2CD62923}" name="xsk2g-hash-at-both" dataDxfId="80">
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,P$2:P$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="16" xr3:uid="{81B15818-6876-A44C-A260-2A604BAEBA82}" name="xsk3g-hash-at-both" dataDxfId="79">
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,Q$2:Q$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="17" xr3:uid="{68EEFDA4-F174-D544-B865-C8873AAC456B}" name="xsk4g-hash-at-both" dataDxfId="78">
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,R$2:R$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="18" xr3:uid="{305EE662-6124-4B43-A625-37C51A44D2EB}" name="max" dataDxfId="77">
+      <calculatedColumnFormula>_xlfn.LET(_xlpm.d,$G23:$R23,MAX(_xlpm.d))</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{C401E4AC-E1BD-4B46-BA1F-009F8AD77F50}" name="Table7" displayName="Table7" ref="B36:R42" totalsRowShown="0">
+  <autoFilter ref="B36:R42" xr:uid="{C401E4AC-E1BD-4B46-BA1F-009F8AD77F50}"/>
+  <tableColumns count="17">
+    <tableColumn id="1" xr3:uid="{56B3EF89-7FD5-B942-BB80-1168A5FD3080}" name="attribute.index"/>
+    <tableColumn id="2" xr3:uid="{B3B6F63C-9DCD-1145-9396-EEA93ED3F654}" name="attribute"/>
+    <tableColumn id="3" xr3:uid="{26C64D56-F266-964B-84C2-81CC0155F159}" name="supplemented"/>
+    <tableColumn id="4" xr3:uid="{3DD6726E-6154-7246-AD5A-A532BFD45820}" name="method.index"/>
+    <tableColumn id="5" xr3:uid="{9EE0ACFE-5BFA-C545-B5E1-8AC65D7DA907}" name="metric"/>
+    <tableColumn id="6" xr3:uid="{B25ED553-0048-354F-8E6A-9CA218DDA650}" name="2g-no-hash" dataDxfId="76">
+      <calculatedColumnFormula>_xlfn.LET(_xlpm.d,$G23:$X23,RANK(G23,_xlpm.d))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{43AF6FE3-AB63-2947-92C1-DFBC7EB0B01C}" name="3g-no-hash" dataDxfId="75">
+      <calculatedColumnFormula>_xlfn.LET(_xlpm.d,$G23:$X23,RANK(H23,_xlpm.d))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{68B4DDFF-FE87-1A4A-8AE5-2D25C1A0F149}" name="4g-no-hash" dataDxfId="74">
+      <calculatedColumnFormula>_xlfn.LET(_xlpm.d,$G23:$X23,RANK(I23,_xlpm.d))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{2660BFF4-80A4-BE42-ABDA-FD0CEC726255}" name="xsk2g-no-hash" dataDxfId="73">
+      <calculatedColumnFormula>_xlfn.LET(_xlpm.d,$G23:$X23,RANK(J23,_xlpm.d))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{EADBDB0B-2F23-484D-B529-BAB92E32C6CF}" name="xsk3g-no-hash" dataDxfId="72">
+      <calculatedColumnFormula>_xlfn.LET(_xlpm.d,$G23:$X23,RANK(K23,_xlpm.d))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="11" xr3:uid="{B5C4D9BB-9BB8-9C44-AEAB-770E9AA3A25C}" name="xsk4g-no-hash" dataDxfId="71">
+      <calculatedColumnFormula>_xlfn.LET(_xlpm.d,$G23:$X23,RANK(L23,_xlpm.d))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="12" xr3:uid="{DB7B33B1-2A72-E84E-BAD1-F7CAC688F8FE}" name="2g-hash-at-both" dataDxfId="70">
+      <calculatedColumnFormula>_xlfn.LET(_xlpm.d,$G23:$X23,RANK(M23,_xlpm.d))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="13" xr3:uid="{6A1E6416-EF0B-7743-B8BA-75D1227DD32C}" name="3g-hash-at-both" dataDxfId="69">
+      <calculatedColumnFormula>_xlfn.LET(_xlpm.d,$G23:$X23,RANK(N23,_xlpm.d))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="14" xr3:uid="{5E6B89E7-58A3-904C-9E47-0E3C51164BB7}" name="4g-hash-at-both" dataDxfId="68">
+      <calculatedColumnFormula>_xlfn.LET(_xlpm.d,$G23:$X23,RANK(O23,_xlpm.d))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="15" xr3:uid="{21219D4A-B484-A546-8EDD-17BC82C048DA}" name="xsk2g-hash-at-both" dataDxfId="67">
+      <calculatedColumnFormula>_xlfn.LET(_xlpm.d,$G23:$X23,RANK(P23,_xlpm.d))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="16" xr3:uid="{3F4A3F78-7141-834C-94FF-F2D1E1F5E38D}" name="xsk3g-hash-at-both" dataDxfId="66">
+      <calculatedColumnFormula>_xlfn.LET(_xlpm.d,$G23:$X23,RANK(Q23,_xlpm.d))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="17" xr3:uid="{7A5E4F7B-263F-8A4C-B443-A6716A44D562}" name="xsk4g-hash-at-both" dataDxfId="65">
+      <calculatedColumnFormula>_xlfn.LET(_xlpm.d,$G23:$X23,RANK(R23,_xlpm.d))</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{C8AA9E6E-9BDF-1C41-9893-B2A889CB478D}" name="Table110" displayName="Table110" ref="A1:S19" totalsRowShown="0">
+  <autoFilter ref="A1:S19" xr:uid="{62C33DBD-BDE4-1C46-98BA-06D036BEAD6C}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S19">
+    <sortCondition ref="B1:B19"/>
+  </sortState>
+  <tableColumns count="19">
+    <tableColumn id="1" xr3:uid="{612E2458-8E74-E246-967D-A1170869A747}" name="lang"/>
+    <tableColumn id="18" xr3:uid="{89A23AED-ED8C-9A49-8C70-5D1DEB97FE73}" name="attribute.index"/>
+    <tableColumn id="2" xr3:uid="{37C7A035-F8C8-5C4E-B4DF-D5CA0A5AA5C0}" name="attribute"/>
+    <tableColumn id="3" xr3:uid="{D031297D-F6F0-F945-A74D-A8BAE29FEE55}" name="supplement"/>
+    <tableColumn id="19" xr3:uid="{2A2BCDDA-0C60-DC40-AF52-00C0532F7B82}" name="method.index"/>
+    <tableColumn id="4" xr3:uid="{19FC2FCD-ECC9-D442-A745-B77EC4D15D13}" name="method"/>
+    <tableColumn id="5" xr3:uid="{61F795D1-9E55-AB44-89F2-30248F7E7921}" name="2g-no-hash" dataDxfId="64"/>
+    <tableColumn id="6" xr3:uid="{BA3712E0-7A40-E642-9775-AE6726A869D6}" name="3g-no-hash" dataDxfId="63"/>
+    <tableColumn id="7" xr3:uid="{3E362E7F-22CE-E54F-9E30-F0DD80594D23}" name="4g-no-hash" dataDxfId="62"/>
+    <tableColumn id="8" xr3:uid="{50A69ACA-7DD9-E64F-9494-40EBEAAAD1C4}" name="xsk2g-no-hash" dataDxfId="61"/>
+    <tableColumn id="9" xr3:uid="{1DE1AB3A-CCB6-3F44-B627-CABF64E6B6F6}" name="xsk3g-no-hash" dataDxfId="60"/>
+    <tableColumn id="10" xr3:uid="{6263A08D-944F-544F-8AEE-E306F3E4ACF4}" name="xsk4g-no-hash" dataDxfId="59"/>
+    <tableColumn id="11" xr3:uid="{3DA6AB8A-AD01-4845-B5BE-43566F03A32A}" name="2g-hash-at-both" dataDxfId="58"/>
+    <tableColumn id="12" xr3:uid="{04215951-6057-AD49-AB22-8B071068C09D}" name="3g-hash-at-both" dataDxfId="57"/>
+    <tableColumn id="13" xr3:uid="{7D4FDBA7-8A34-9D44-B243-20E6BC181153}" name="4g-hash-at-both" dataDxfId="56"/>
+    <tableColumn id="14" xr3:uid="{FE537402-E705-644F-A11E-E90E23B298C0}" name="xsk2g-hash-at-both" dataDxfId="55"/>
+    <tableColumn id="15" xr3:uid="{9C1F0C1D-19D8-8A46-92D0-540EE49FE079}" name="xsk3g-hash-at-both" dataDxfId="54"/>
+    <tableColumn id="16" xr3:uid="{5F8AA456-A2ED-E54A-9ACC-D43290DC1953}" name="xsk4g-hash-at-both" dataDxfId="53"/>
+    <tableColumn id="17" xr3:uid="{018C34F6-72C5-2547-9484-230A2CCDD554}" name="max" dataDxfId="52">
+      <calculatedColumnFormula>_xlfn.LET(_xlpm.d,$G2:$R2,MAX(_xlpm.d))</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{E6E828DD-BAE1-0D41-B9FF-3A80A0F38066}" name="Table11" displayName="Table11" ref="B22:S28" totalsRowShown="0" headerRowDxfId="51">
+  <autoFilter ref="B22:S28" xr:uid="{E6E828DD-BAE1-0D41-B9FF-3A80A0F38066}"/>
+  <tableColumns count="18">
+    <tableColumn id="1" xr3:uid="{06BBAFA8-30C7-C943-B7B1-4D009BACCC00}" name="attribute.index"/>
+    <tableColumn id="2" xr3:uid="{04BDCF93-74B8-CC4A-A151-23AC2D697B6F}" name="attribute"/>
+    <tableColumn id="3" xr3:uid="{3F09466F-54C9-334F-8E20-CCCABE1373DF}" name="supplemented"/>
+    <tableColumn id="4" xr3:uid="{E8A38307-6316-0041-B295-75A92A0187E6}" name="method.index"/>
+    <tableColumn id="5" xr3:uid="{28286CCA-7DD9-D94A-A25C-AB2EC960B357}" name="metric"/>
+    <tableColumn id="6" xr3:uid="{C942D0AF-F8A3-1043-984F-2D0BE85CFC51}" name="2g-no-hash" dataDxfId="50">
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,G$2:G$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{46AAE389-CF33-4B4D-B11D-699824564800}" name="3g-no-hash" dataDxfId="49">
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,H$2:H$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{C2427AF7-1AE5-5947-BB1C-45E6E7B9E7ED}" name="4g-no-hash" dataDxfId="48">
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,I$2:I$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{ED956FEA-5A7D-4A45-915C-BCF1582E2B9D}" name="xsk2g-no-hash" dataDxfId="47">
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,J$2:J$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{A7300332-F14F-DA4D-BD71-A77BDE7F01B2}" name="xsk3g-no-hash" dataDxfId="46">
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,K$2:K$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="11" xr3:uid="{F73D60C9-BB5E-3D4E-94A3-85A2A6240EE4}" name="xsk4g-no-hash" dataDxfId="45">
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,L$2:L$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="12" xr3:uid="{9D8FFDA0-8AC1-C44C-878E-9D27D35F7960}" name="2g-hash-at-both" dataDxfId="44">
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,M$2:M$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="13" xr3:uid="{74B5B9B3-D509-8844-9208-5E11B511B031}" name="3g-hash-at-both" dataDxfId="43">
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,N$2:N$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="14" xr3:uid="{9B9CBD0C-6763-7042-A123-E3282BC788CB}" name="4g-hash-at-both" dataDxfId="42">
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,O$2:O$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="15" xr3:uid="{BCA72DE9-CE40-BA4D-80A7-D3D2D6BC2FA4}" name="xsk2g-hash-at-both" dataDxfId="41">
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,P$2:P$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="16" xr3:uid="{48136231-ABB5-C84B-A976-63BF06D63B16}" name="xsk3g-hash-at-both" dataDxfId="40">
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,Q$2:Q$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="17" xr3:uid="{4564DDDC-A2E5-E648-ADD7-2806FEF7A95B}" name="xsk4g-hash-at-both" dataDxfId="39">
+      <calculatedColumnFormula array="1">_xlfn.LET(_xlpm.d,R$2:R$19,_xlpm.a,$C$2:$C$19=$C23,_xlpm.b,$D$2:$D$19=$D23,MAX(_xlfn._xlws.FILTER(_xlpm.d,_xlpm.a*_xlpm.b)))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="18" xr3:uid="{EF6262A8-36CD-B94D-84E3-31FF184250FF}" name="max" dataDxfId="38">
+      <calculatedColumnFormula>_xlfn.LET(_xlpm.d,$G23:$R23,MAX(_xlpm.d))</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{20CFC09F-4CA7-5A4B-8710-2254971E0D64}" name="Table3" displayName="Table3" ref="A1:S19" totalsRowShown="0">
+  <autoFilter ref="A1:S19" xr:uid="{20CFC09F-4CA7-5A4B-8710-2254971E0D64}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S19">
+    <sortCondition ref="B1:B19"/>
+  </sortState>
+  <tableColumns count="19">
+    <tableColumn id="1" xr3:uid="{BF35C7E1-BA33-8348-81F9-C57324460597}" name="lang"/>
+    <tableColumn id="2" xr3:uid="{D5E39B1A-2425-1D4E-BC5B-18BE3E7E6660}" name="attribute.index"/>
+    <tableColumn id="3" xr3:uid="{6BAA365A-F6C8-5D4C-8F01-4A53503BDC88}" name="attribute"/>
+    <tableColumn id="4" xr3:uid="{584BAD1A-9B8E-0547-96D9-A92A5A8DE50C}" name="supplement"/>
+    <tableColumn id="5" xr3:uid="{9A00C24F-08E3-E844-B5A6-E2D6D4403A02}" name="method.index"/>
+    <tableColumn id="6" xr3:uid="{FAC137F9-992F-F84A-8FEB-6E306FB9B6B7}" name="method"/>
+    <tableColumn id="7" xr3:uid="{B0EA0C28-58A7-7847-A0A3-D5CED943EFC0}" name="2g-no-hash" dataDxfId="37"/>
+    <tableColumn id="8" xr3:uid="{EA3E43C7-1764-C347-A3E2-7D20096614E3}" name="3g-no-hash" dataDxfId="36"/>
+    <tableColumn id="9" xr3:uid="{908B93EF-68ED-B840-9D06-53E9DA28FADB}" name="4g-no-hash" dataDxfId="35"/>
+    <tableColumn id="10" xr3:uid="{A5CA07AC-2A66-C543-B13E-DD6CE094F3E3}" name="xsk2g-no-hash" dataDxfId="34"/>
+    <tableColumn id="11" xr3:uid="{26A5F9ED-F6B2-134F-B1DC-AC26E155B105}" name="xsk3g-no-hash" dataDxfId="33"/>
+    <tableColumn id="12" xr3:uid="{F47EE545-5E10-4848-BD75-A72E0AFE04AB}" name="xsk4g-no-hash" dataDxfId="32"/>
+    <tableColumn id="13" xr3:uid="{AE7DBC1B-0B86-6844-A15A-A2602343D372}" name="2g-hash-at-both" dataDxfId="31"/>
+    <tableColumn id="14" xr3:uid="{465F812F-73F8-8548-9144-04C25B3C278A}" name="3g-hash-at-both" dataDxfId="30"/>
+    <tableColumn id="15" xr3:uid="{71E8F9E2-32E5-CC4E-A9B4-9BEB76A59277}" name="4g-hash-at-both" dataDxfId="29"/>
+    <tableColumn id="16" xr3:uid="{8AD668A4-7E49-9443-ABE3-AA6A4B0AE83D}" name="xsk2g-hash-at-both" dataDxfId="28"/>
+    <tableColumn id="17" xr3:uid="{861BBDFD-B295-FF44-9C9A-F8A1E16A6DDC}" name="xsk3g-hash-at-both" dataDxfId="27"/>
+    <tableColumn id="18" xr3:uid="{1A3A42F7-BD1E-504A-B956-CBC1CB0D9385}" name="xsk4g-hash-at-both" dataDxfId="26"/>
+    <tableColumn id="19" xr3:uid="{48EA1203-65AC-F84A-9C85-DD4C4DAE1843}" name="max" dataDxfId="25">
+      <calculatedColumnFormula>_xlfn.LET(_xlpm.d,$G2:$R2,MAX(_xlpm.d))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -11678,19 +6692,19 @@
   <sheetData>
     <row r="1" spans="1:24" ht="25" customHeight="1">
       <c r="A1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" t="s">
         <v>35</v>
-      </c>
-      <c r="E1" t="s">
-        <v>36</v>
       </c>
       <c r="F1" t="s">
         <v>23</v>
@@ -11708,7 +6722,7 @@
         <v>27</v>
       </c>
       <c r="K1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L1" t="s">
         <v>4</v>
@@ -11752,13 +6766,13 @@
     </row>
     <row r="2" spans="1:24" ht="25" customHeight="1">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B2">
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D2">
         <v>1.2</v>
@@ -11827,13 +6841,13 @@
     </row>
     <row r="3" spans="1:24" ht="25" customHeight="1">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D3">
         <v>1.2</v>
@@ -11902,13 +6916,13 @@
     </row>
     <row r="4" spans="1:24" ht="25" customHeight="1">
       <c r="A4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B4">
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D4">
         <v>1.2</v>
@@ -11977,13 +6991,13 @@
     </row>
     <row r="5" spans="1:24" ht="25" customHeight="1">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5">
         <v>1.2</v>
@@ -12052,13 +7066,13 @@
     </row>
     <row r="6" spans="1:24" ht="25" customHeight="1">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6">
         <v>1.2</v>
@@ -12127,13 +7141,13 @@
     </row>
     <row r="7" spans="1:24" ht="25" customHeight="1">
       <c r="A7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D7">
         <v>1.2</v>
@@ -12202,13 +7216,13 @@
     </row>
     <row r="8" spans="1:24" ht="25" customHeight="1">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D8">
         <v>2</v>
@@ -12277,13 +7291,13 @@
     </row>
     <row r="9" spans="1:24" ht="25" customHeight="1">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -12352,13 +7366,13 @@
     </row>
     <row r="10" spans="1:24" ht="25" customHeight="1">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D10">
         <v>2</v>
@@ -12385,55 +7399,55 @@
         <f>_xlfn.LET(_xlpm.ml,_xlfn.SINGLE(Table6[ml]),_xlpm.sn,_xlfn.SINGLE(Table6[sample.n]),_xlpm.spl,_xlfn.SINGLE(Table6[supplemented]),_xlpm.mgv,_xlfn.SINGLE(Table6[mgv]),_xlpm.attr,_xlfn.SINGLE(Table6[attribute]),_xlfn.TEXTJOIN({"-ml:","-suppl:","-mgv:","-sn:",""},TRUE,LEFT(_xlpm.attr,3),_xlpm.ml,LEFT(_xlpm.spl,1),_xlpm.mgv,_xlpm.sn,"k"))</f>
         <v>gen-ml:2-suppl:F-mgv:9-sn:2k</v>
       </c>
-      <c r="L10" s="12">
+      <c r="L10" s="7">
         <v>0.69</v>
       </c>
-      <c r="M10" s="12">
+      <c r="M10" s="7">
         <v>0.69</v>
       </c>
-      <c r="N10" s="12">
+      <c r="N10" s="7">
         <v>0.6</v>
       </c>
-      <c r="O10" s="12">
+      <c r="O10" s="7">
         <v>0.65</v>
       </c>
-      <c r="P10" s="12">
+      <c r="P10" s="7">
         <v>0.59</v>
       </c>
-      <c r="Q10" s="12">
+      <c r="Q10" s="7">
         <v>0.66</v>
       </c>
-      <c r="R10" s="12">
+      <c r="R10" s="7">
         <v>0.61</v>
       </c>
-      <c r="S10" s="12">
+      <c r="S10" s="7">
         <v>0.66</v>
       </c>
-      <c r="T10" s="12">
+      <c r="T10" s="7">
         <v>0.69</v>
       </c>
-      <c r="U10" s="12">
+      <c r="U10" s="7">
         <v>0.65</v>
       </c>
-      <c r="V10" s="12">
+      <c r="V10" s="7">
         <v>0.64</v>
       </c>
-      <c r="W10" s="12">
+      <c r="W10" s="7">
         <v>0.66</v>
       </c>
-      <c r="X10" s="12">
+      <c r="X10" s="7">
         <v>0.69</v>
       </c>
     </row>
     <row r="11" spans="1:24" ht="25" customHeight="1">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B11">
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D11">
         <v>2</v>
@@ -12460,55 +7474,55 @@
         <f>_xlfn.LET(_xlpm.ml,_xlfn.SINGLE(Table6[ml]),_xlpm.sn,_xlfn.SINGLE(Table6[sample.n]),_xlpm.spl,_xlfn.SINGLE(Table6[supplemented]),_xlpm.mgv,_xlfn.SINGLE(Table6[mgv]),_xlpm.attr,_xlfn.SINGLE(Table6[attribute]),_xlfn.TEXTJOIN({"-ml:","-suppl:","-mgv:","-sn:",""},TRUE,LEFT(_xlpm.attr,3),_xlpm.ml,LEFT(_xlpm.spl,1),_xlpm.mgv,_xlpm.sn,"k"))</f>
         <v>gen-ml:2-suppl:T-mgv:9-sn:2k</v>
       </c>
-      <c r="L11" s="12">
+      <c r="L11" s="7">
         <v>0.67</v>
       </c>
-      <c r="M11" s="12">
+      <c r="M11" s="7">
         <v>0.69</v>
       </c>
-      <c r="N11" s="12">
+      <c r="N11" s="7">
         <v>0.65</v>
       </c>
-      <c r="O11" s="12">
+      <c r="O11" s="7">
         <v>0.67</v>
       </c>
-      <c r="P11" s="12">
+      <c r="P11" s="7">
         <v>0.6</v>
       </c>
-      <c r="Q11" s="12">
+      <c r="Q11" s="7">
         <v>0.69</v>
       </c>
-      <c r="R11" s="12">
+      <c r="R11" s="7">
         <v>0.66</v>
       </c>
-      <c r="S11" s="12">
+      <c r="S11" s="7">
         <v>0.69</v>
       </c>
-      <c r="T11" s="12">
+      <c r="T11" s="7">
         <v>0.73</v>
       </c>
-      <c r="U11" s="12">
+      <c r="U11" s="7">
         <v>0.64</v>
       </c>
-      <c r="V11" s="12">
+      <c r="V11" s="7">
         <v>0.67</v>
       </c>
-      <c r="W11" s="12">
+      <c r="W11" s="7">
         <v>0.62</v>
       </c>
-      <c r="X11" s="12">
+      <c r="X11" s="7">
         <v>0.73</v>
       </c>
     </row>
     <row r="12" spans="1:24" ht="25" customHeight="1">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12">
         <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D12">
         <v>2</v>
@@ -12535,55 +7549,55 @@
         <f>_xlfn.LET(_xlpm.ml,_xlfn.SINGLE(Table6[ml]),_xlpm.sn,_xlfn.SINGLE(Table6[sample.n]),_xlpm.spl,_xlfn.SINGLE(Table6[supplemented]),_xlpm.mgv,_xlfn.SINGLE(Table6[mgv]),_xlpm.attr,_xlfn.SINGLE(Table6[attribute]),_xlfn.TEXTJOIN({"-ml:","-suppl:","-mgv:","-sn:",""},TRUE,LEFT(_xlpm.attr,3),_xlpm.ml,LEFT(_xlpm.spl,1),_xlpm.mgv,_xlpm.sn,"k"))</f>
         <v>cas-ml:2-suppl:F-mgv:9-sn:2k</v>
       </c>
-      <c r="L12" s="12">
+      <c r="L12" s="7">
         <v>0.42</v>
       </c>
-      <c r="M12" s="12">
+      <c r="M12" s="7">
         <v>0.5</v>
       </c>
-      <c r="N12" s="12">
+      <c r="N12" s="7">
         <v>0.45</v>
       </c>
-      <c r="O12" s="12">
+      <c r="O12" s="7">
         <v>0.46</v>
       </c>
-      <c r="P12" s="12">
+      <c r="P12" s="7">
         <v>0.53</v>
       </c>
-      <c r="Q12" s="12">
+      <c r="Q12" s="7">
         <v>0.45</v>
       </c>
-      <c r="R12" s="12">
+      <c r="R12" s="7">
         <v>0.42</v>
       </c>
-      <c r="S12" s="12">
+      <c r="S12" s="7">
         <v>0.43</v>
       </c>
-      <c r="T12" s="12">
+      <c r="T12" s="7">
         <v>0.44</v>
       </c>
-      <c r="U12" s="12">
+      <c r="U12" s="7">
         <v>0.4</v>
       </c>
-      <c r="V12" s="12">
+      <c r="V12" s="7">
         <v>0.43</v>
       </c>
-      <c r="W12" s="12">
+      <c r="W12" s="7">
         <v>0.47</v>
       </c>
-      <c r="X12" s="12">
+      <c r="X12" s="7">
         <v>0.53</v>
       </c>
     </row>
     <row r="13" spans="1:24" ht="25" customHeight="1">
       <c r="A13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -12610,55 +7624,55 @@
         <f>_xlfn.LET(_xlpm.ml,_xlfn.SINGLE(Table6[ml]),_xlpm.sn,_xlfn.SINGLE(Table6[sample.n]),_xlpm.spl,_xlfn.SINGLE(Table6[supplemented]),_xlpm.mgv,_xlfn.SINGLE(Table6[mgv]),_xlpm.attr,_xlfn.SINGLE(Table6[attribute]),_xlfn.TEXTJOIN({"-ml:","-suppl:","-mgv:","-sn:",""},TRUE,LEFT(_xlpm.attr,3),_xlpm.ml,LEFT(_xlpm.spl,1),_xlpm.mgv,_xlpm.sn,"k"))</f>
         <v>cas-ml:2-suppl:T-mgv:9-sn:2k</v>
       </c>
-      <c r="L13" s="12">
+      <c r="L13" s="7">
         <v>0.55000000000000004</v>
       </c>
-      <c r="M13" s="12">
+      <c r="M13" s="7">
         <v>0.6</v>
       </c>
-      <c r="N13" s="12">
+      <c r="N13" s="7">
         <v>0.55000000000000004</v>
       </c>
-      <c r="O13" s="12">
+      <c r="O13" s="7">
         <v>0.52</v>
       </c>
-      <c r="P13" s="12">
+      <c r="P13" s="7">
         <v>0.54</v>
       </c>
-      <c r="Q13" s="12">
+      <c r="Q13" s="7">
         <v>0.54</v>
       </c>
-      <c r="R13" s="12">
+      <c r="R13" s="7">
         <v>0.55000000000000004</v>
       </c>
-      <c r="S13" s="12">
+      <c r="S13" s="7">
         <v>0.56000000000000005</v>
       </c>
-      <c r="T13" s="12">
+      <c r="T13" s="7">
         <v>0.49</v>
       </c>
-      <c r="U13" s="12">
+      <c r="U13" s="7">
         <v>0.47</v>
       </c>
-      <c r="V13" s="12">
+      <c r="V13" s="7">
         <v>0.51</v>
       </c>
-      <c r="W13" s="12">
+      <c r="W13" s="7">
         <v>0.54</v>
       </c>
-      <c r="X13" s="12">
+      <c r="X13" s="7">
         <v>0.6</v>
       </c>
     </row>
     <row r="14" spans="1:24" ht="25" customHeight="1">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B14">
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D14">
         <v>1.2</v>
@@ -12727,13 +7741,13 @@
     </row>
     <row r="15" spans="1:24" ht="25" customHeight="1">
       <c r="A15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B15">
         <v>3</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D15">
         <v>1.2</v>
@@ -12802,13 +7816,13 @@
     </row>
     <row r="16" spans="1:24" ht="25" customHeight="1">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B16">
         <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D16">
         <v>1.2</v>
@@ -12835,55 +7849,55 @@
         <f>_xlfn.LET(_xlpm.ml,_xlfn.SINGLE(Table6[ml]),_xlpm.sn,_xlfn.SINGLE(Table6[sample.n]),_xlpm.spl,_xlfn.SINGLE(Table6[supplemented]),_xlpm.mgv,_xlfn.SINGLE(Table6[mgv]),_xlpm.attr,_xlfn.SINGLE(Table6[attribute]),_xlfn.TEXTJOIN({"-ml:","-suppl:","-mgv:","-sn:",""},TRUE,LEFT(_xlpm.attr,3),_xlpm.ml,LEFT(_xlpm.spl,1),_xlpm.mgv,_xlpm.sn,"k"))</f>
         <v>gen-ml:3-suppl:F-mgv:9-sn:1.2k</v>
       </c>
-      <c r="L16" s="12">
+      <c r="L16" s="7">
         <v>0.53</v>
       </c>
-      <c r="M16" s="12">
+      <c r="M16" s="7">
         <v>0.56000000000000005</v>
       </c>
-      <c r="N16" s="12">
+      <c r="N16" s="7">
         <v>0.62</v>
       </c>
-      <c r="O16" s="12">
+      <c r="O16" s="7">
         <v>0.61</v>
       </c>
-      <c r="P16" s="12">
+      <c r="P16" s="7">
         <v>0.57999999999999996</v>
       </c>
-      <c r="Q16" s="12">
+      <c r="Q16" s="7">
         <v>0.6</v>
       </c>
-      <c r="R16" s="12">
+      <c r="R16" s="7">
         <v>0.62</v>
       </c>
-      <c r="S16" s="12">
+      <c r="S16" s="7">
         <v>0.63</v>
       </c>
-      <c r="T16" s="12">
+      <c r="T16" s="7">
         <v>0.68</v>
       </c>
-      <c r="U16" s="12">
+      <c r="U16" s="7">
         <v>0.64</v>
       </c>
-      <c r="V16" s="12">
+      <c r="V16" s="7">
         <v>0.6</v>
       </c>
-      <c r="W16" s="12">
+      <c r="W16" s="7">
         <v>0.53</v>
       </c>
-      <c r="X16" s="12">
+      <c r="X16" s="7">
         <v>0.68</v>
       </c>
     </row>
     <row r="17" spans="1:24" ht="25" customHeight="1">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B17">
         <v>3</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D17">
         <v>1.2</v>
@@ -12910,55 +7924,55 @@
         <f>_xlfn.LET(_xlpm.ml,_xlfn.SINGLE(Table6[ml]),_xlpm.sn,_xlfn.SINGLE(Table6[sample.n]),_xlpm.spl,_xlfn.SINGLE(Table6[supplemented]),_xlpm.mgv,_xlfn.SINGLE(Table6[mgv]),_xlpm.attr,_xlfn.SINGLE(Table6[attribute]),_xlfn.TEXTJOIN({"-ml:","-suppl:","-mgv:","-sn:",""},TRUE,LEFT(_xlpm.attr,3),_xlpm.ml,LEFT(_xlpm.spl,1),_xlpm.mgv,_xlpm.sn,"k"))</f>
         <v>gen-ml:3-suppl:T-mgv:9-sn:1.2k</v>
       </c>
-      <c r="L17" s="12">
+      <c r="L17" s="7">
         <v>0.55000000000000004</v>
       </c>
-      <c r="M17" s="12">
+      <c r="M17" s="7">
         <v>0.57999999999999996</v>
       </c>
-      <c r="N17" s="12">
+      <c r="N17" s="7">
         <v>0.68</v>
       </c>
-      <c r="O17" s="12">
+      <c r="O17" s="7">
         <v>0.63</v>
       </c>
-      <c r="P17" s="12">
+      <c r="P17" s="7">
         <v>0.65</v>
       </c>
-      <c r="Q17" s="12">
+      <c r="Q17" s="7">
         <v>0.6</v>
       </c>
-      <c r="R17" s="12">
+      <c r="R17" s="7">
         <v>0.7</v>
       </c>
-      <c r="S17" s="12">
+      <c r="S17" s="7">
         <v>0.68</v>
       </c>
-      <c r="T17" s="12">
+      <c r="T17" s="7">
         <v>0.69</v>
       </c>
-      <c r="U17" s="12">
+      <c r="U17" s="7">
         <v>0.71</v>
       </c>
-      <c r="V17" s="12">
+      <c r="V17" s="7">
         <v>0.57999999999999996</v>
       </c>
-      <c r="W17" s="12">
+      <c r="W17" s="7">
         <v>0.51</v>
       </c>
-      <c r="X17" s="12">
+      <c r="X17" s="7">
         <v>0.71</v>
       </c>
     </row>
     <row r="18" spans="1:24" ht="25" customHeight="1">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B18">
         <v>3</v>
       </c>
       <c r="C18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D18">
         <v>1.2</v>
@@ -12985,55 +7999,55 @@
         <f>_xlfn.LET(_xlpm.ml,_xlfn.SINGLE(Table6[ml]),_xlpm.sn,_xlfn.SINGLE(Table6[sample.n]),_xlpm.spl,_xlfn.SINGLE(Table6[supplemented]),_xlpm.mgv,_xlfn.SINGLE(Table6[mgv]),_xlpm.attr,_xlfn.SINGLE(Table6[attribute]),_xlfn.TEXTJOIN({"-ml:","-suppl:","-mgv:","-sn:",""},TRUE,LEFT(_xlpm.attr,3),_xlpm.ml,LEFT(_xlpm.spl,1),_xlpm.mgv,_xlpm.sn,"k"))</f>
         <v>cas-ml:3-suppl:F-mgv:9-sn:1.2k</v>
       </c>
-      <c r="L18" s="12">
+      <c r="L18" s="7">
         <v>0.36</v>
       </c>
-      <c r="M18" s="12">
+      <c r="M18" s="7">
         <v>0.42</v>
       </c>
-      <c r="N18" s="12">
+      <c r="N18" s="7">
         <v>0.47</v>
       </c>
-      <c r="O18" s="12">
+      <c r="O18" s="7">
         <v>0.39</v>
       </c>
-      <c r="P18" s="12">
+      <c r="P18" s="7">
         <v>0.44</v>
       </c>
-      <c r="Q18" s="12">
+      <c r="Q18" s="7">
         <v>0.45</v>
       </c>
-      <c r="R18" s="12">
+      <c r="R18" s="7">
         <v>0.38</v>
       </c>
-      <c r="S18" s="12">
+      <c r="S18" s="7">
         <v>0.35</v>
       </c>
-      <c r="T18" s="12">
+      <c r="T18" s="7">
         <v>0.42</v>
       </c>
-      <c r="U18" s="12">
+      <c r="U18" s="7">
         <v>0.41</v>
       </c>
-      <c r="V18" s="12">
+      <c r="V18" s="7">
         <v>0.39</v>
       </c>
-      <c r="W18" s="12">
+      <c r="W18" s="7">
         <v>0.48</v>
       </c>
-      <c r="X18" s="12">
+      <c r="X18" s="7">
         <v>0.48</v>
       </c>
     </row>
     <row r="19" spans="1:24" ht="25" customHeight="1">
       <c r="A19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B19">
         <v>3</v>
       </c>
       <c r="C19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D19">
         <v>1.2</v>
@@ -13060,55 +8074,55 @@
         <f>_xlfn.LET(_xlpm.ml,_xlfn.SINGLE(Table6[ml]),_xlpm.sn,_xlfn.SINGLE(Table6[sample.n]),_xlpm.spl,_xlfn.SINGLE(Table6[supplemented]),_xlpm.mgv,_xlfn.SINGLE(Table6[mgv]),_xlpm.attr,_xlfn.SINGLE(Table6[attribute]),_xlfn.TEXTJOIN({"-ml:","-suppl:","-mgv:","-sn:",""},TRUE,LEFT(_xlpm.attr,3),_xlpm.ml,LEFT(_xlpm.spl,1),_xlpm.mgv,_xlpm.sn,"k"))</f>
         <v>cas-ml:3-suppl:T-mgv:9-sn:1.2k</v>
       </c>
-      <c r="L19" s="12">
+      <c r="L19" s="7">
         <v>0.45</v>
       </c>
-      <c r="M19" s="12">
+      <c r="M19" s="7">
         <v>0.54</v>
       </c>
-      <c r="N19" s="12">
+      <c r="N19" s="7">
         <v>0.62</v>
       </c>
-      <c r="O19" s="12">
+      <c r="O19" s="7">
         <v>0.49</v>
       </c>
-      <c r="P19" s="12">
+      <c r="P19" s="7">
         <v>0.47</v>
       </c>
-      <c r="Q19" s="12">
+      <c r="Q19" s="7">
         <v>0.47</v>
       </c>
-      <c r="R19" s="12">
+      <c r="R19" s="7">
         <v>0.5</v>
       </c>
-      <c r="S19" s="12">
+      <c r="S19" s="7">
         <v>0.46</v>
       </c>
-      <c r="T19" s="12">
+      <c r="T19" s="7">
         <v>0.53</v>
       </c>
-      <c r="U19" s="12">
+      <c r="U19" s="7">
         <v>0.43</v>
       </c>
-      <c r="V19" s="12">
+      <c r="V19" s="7">
         <v>0.45</v>
       </c>
-      <c r="W19" s="12">
+      <c r="W19" s="7">
         <v>0.51</v>
       </c>
-      <c r="X19" s="12">
+      <c r="X19" s="7">
         <v>0.62</v>
       </c>
     </row>
     <row r="20" spans="1:24" ht="25" customHeight="1">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B20">
         <v>3</v>
       </c>
       <c r="C20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D20">
         <v>2</v>
@@ -13177,13 +8191,13 @@
     </row>
     <row r="21" spans="1:24" ht="25" customHeight="1">
       <c r="A21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B21">
         <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D21">
         <v>2</v>
@@ -13252,13 +8266,13 @@
     </row>
     <row r="22" spans="1:24" ht="25" customHeight="1">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B22">
         <v>3</v>
       </c>
       <c r="C22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D22">
         <v>2</v>
@@ -13285,55 +8299,55 @@
         <f>_xlfn.LET(_xlpm.ml,_xlfn.SINGLE(Table6[ml]),_xlpm.sn,_xlfn.SINGLE(Table6[sample.n]),_xlpm.spl,_xlfn.SINGLE(Table6[supplemented]),_xlpm.mgv,_xlfn.SINGLE(Table6[mgv]),_xlpm.attr,_xlfn.SINGLE(Table6[attribute]),_xlfn.TEXTJOIN({"-ml:","-suppl:","-mgv:","-sn:",""},TRUE,LEFT(_xlpm.attr,3),_xlpm.ml,LEFT(_xlpm.spl,1),_xlpm.mgv,_xlpm.sn,"k"))</f>
         <v>gen-ml:3-suppl:F-mgv:9-sn:2k</v>
       </c>
-      <c r="L22" s="12">
+      <c r="L22" s="7">
         <v>0.69</v>
       </c>
-      <c r="M22" s="12">
+      <c r="M22" s="7">
         <v>0.69</v>
       </c>
-      <c r="N22" s="12">
+      <c r="N22" s="7">
         <v>0.6</v>
       </c>
-      <c r="O22" s="12">
+      <c r="O22" s="7">
         <v>0.65</v>
       </c>
-      <c r="P22" s="12">
+      <c r="P22" s="7">
         <v>0.59</v>
       </c>
-      <c r="Q22" s="12">
+      <c r="Q22" s="7">
         <v>0.66</v>
       </c>
-      <c r="R22" s="12">
+      <c r="R22" s="7">
         <v>0.61</v>
       </c>
-      <c r="S22" s="12">
+      <c r="S22" s="7">
         <v>0.66</v>
       </c>
-      <c r="T22" s="12">
+      <c r="T22" s="7">
         <v>0.69</v>
       </c>
-      <c r="U22" s="12">
+      <c r="U22" s="7">
         <v>0.65</v>
       </c>
-      <c r="V22" s="12">
+      <c r="V22" s="7">
         <v>0.64</v>
       </c>
-      <c r="W22" s="12">
+      <c r="W22" s="7">
         <v>0.66</v>
       </c>
-      <c r="X22" s="12">
+      <c r="X22" s="7">
         <v>0.69</v>
       </c>
     </row>
     <row r="23" spans="1:24" ht="25" customHeight="1">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23">
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D23">
         <v>2</v>
@@ -13360,55 +8374,55 @@
         <f>_xlfn.LET(_xlpm.ml,_xlfn.SINGLE(Table6[ml]),_xlpm.sn,_xlfn.SINGLE(Table6[sample.n]),_xlpm.spl,_xlfn.SINGLE(Table6[supplemented]),_xlpm.mgv,_xlfn.SINGLE(Table6[mgv]),_xlpm.attr,_xlfn.SINGLE(Table6[attribute]),_xlfn.TEXTJOIN({"-ml:","-suppl:","-mgv:","-sn:",""},TRUE,LEFT(_xlpm.attr,3),_xlpm.ml,LEFT(_xlpm.spl,1),_xlpm.mgv,_xlpm.sn,"k"))</f>
         <v>gen-ml:3-suppl:T-mgv:9-sn:2k</v>
       </c>
-      <c r="L23" s="12">
+      <c r="L23" s="7">
         <v>0.67</v>
       </c>
-      <c r="M23" s="12">
+      <c r="M23" s="7">
         <v>0.69</v>
       </c>
-      <c r="N23" s="12">
+      <c r="N23" s="7">
         <v>0.65</v>
       </c>
-      <c r="O23" s="12">
+      <c r="O23" s="7">
         <v>0.67</v>
       </c>
-      <c r="P23" s="12">
+      <c r="P23" s="7">
         <v>0.6</v>
       </c>
-      <c r="Q23" s="12">
+      <c r="Q23" s="7">
         <v>0.69</v>
       </c>
-      <c r="R23" s="12">
+      <c r="R23" s="7">
         <v>0.66</v>
       </c>
-      <c r="S23" s="12">
+      <c r="S23" s="7">
         <v>0.69</v>
       </c>
-      <c r="T23" s="12">
+      <c r="T23" s="7">
         <v>0.73</v>
       </c>
-      <c r="U23" s="12">
+      <c r="U23" s="7">
         <v>0.64</v>
       </c>
-      <c r="V23" s="12">
+      <c r="V23" s="7">
         <v>0.67</v>
       </c>
-      <c r="W23" s="12">
+      <c r="W23" s="7">
         <v>0.62</v>
       </c>
-      <c r="X23" s="12">
+      <c r="X23" s="7">
         <v>0.73</v>
       </c>
     </row>
     <row r="24" spans="1:24" ht="25" customHeight="1">
       <c r="A24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B24">
         <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D24">
         <v>2</v>
@@ -13435,55 +8449,55 @@
         <f>_xlfn.LET(_xlpm.ml,_xlfn.SINGLE(Table6[ml]),_xlpm.sn,_xlfn.SINGLE(Table6[sample.n]),_xlpm.spl,_xlfn.SINGLE(Table6[supplemented]),_xlpm.mgv,_xlfn.SINGLE(Table6[mgv]),_xlpm.attr,_xlfn.SINGLE(Table6[attribute]),_xlfn.TEXTJOIN({"-ml:","-suppl:","-mgv:","-sn:",""},TRUE,LEFT(_xlpm.attr,3),_xlpm.ml,LEFT(_xlpm.spl,1),_xlpm.mgv,_xlpm.sn,"k"))</f>
         <v>cas-ml:3-suppl:F-mgv:9-sn:2k</v>
       </c>
-      <c r="L24" s="12">
+      <c r="L24" s="7">
         <v>0.42</v>
       </c>
-      <c r="M24" s="12">
+      <c r="M24" s="7">
         <v>0.5</v>
       </c>
-      <c r="N24" s="12">
+      <c r="N24" s="7">
         <v>0.45</v>
       </c>
-      <c r="O24" s="12">
+      <c r="O24" s="7">
         <v>0.46</v>
       </c>
-      <c r="P24" s="12">
+      <c r="P24" s="7">
         <v>0.53</v>
       </c>
-      <c r="Q24" s="12">
+      <c r="Q24" s="7">
         <v>0.45</v>
       </c>
-      <c r="R24" s="12">
+      <c r="R24" s="7">
         <v>0.42</v>
       </c>
-      <c r="S24" s="12">
+      <c r="S24" s="7">
         <v>0.43</v>
       </c>
-      <c r="T24" s="12">
+      <c r="T24" s="7">
         <v>0.44</v>
       </c>
-      <c r="U24" s="12">
+      <c r="U24" s="7">
         <v>0.4</v>
       </c>
-      <c r="V24" s="12">
+      <c r="V24" s="7">
         <v>0.43</v>
       </c>
-      <c r="W24" s="12">
+      <c r="W24" s="7">
         <v>0.47</v>
       </c>
-      <c r="X24" s="12">
+      <c r="X24" s="7">
         <v>0.53</v>
       </c>
     </row>
     <row r="25" spans="1:24" ht="25" customHeight="1">
       <c r="A25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B25">
         <v>3</v>
       </c>
       <c r="C25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D25">
         <v>2</v>
@@ -13510,43 +8524,43 @@
         <f>_xlfn.LET(_xlpm.ml,_xlfn.SINGLE(Table6[ml]),_xlpm.sn,_xlfn.SINGLE(Table6[sample.n]),_xlpm.spl,_xlfn.SINGLE(Table6[supplemented]),_xlpm.mgv,_xlfn.SINGLE(Table6[mgv]),_xlpm.attr,_xlfn.SINGLE(Table6[attribute]),_xlfn.TEXTJOIN({"-ml:","-suppl:","-mgv:","-sn:",""},TRUE,LEFT(_xlpm.attr,3),_xlpm.ml,LEFT(_xlpm.spl,1),_xlpm.mgv,_xlpm.sn,"k"))</f>
         <v>cas-ml:3-suppl:T-mgv:9-sn:2k</v>
       </c>
-      <c r="L25" s="12">
+      <c r="L25" s="7">
         <v>0.55000000000000004</v>
       </c>
-      <c r="M25" s="12">
+      <c r="M25" s="7">
         <v>0.6</v>
       </c>
-      <c r="N25" s="12">
+      <c r="N25" s="7">
         <v>0.55000000000000004</v>
       </c>
-      <c r="O25" s="12">
+      <c r="O25" s="7">
         <v>0.52</v>
       </c>
-      <c r="P25" s="12">
+      <c r="P25" s="7">
         <v>0.54</v>
       </c>
-      <c r="Q25" s="12">
+      <c r="Q25" s="7">
         <v>0.54</v>
       </c>
-      <c r="R25" s="12">
+      <c r="R25" s="7">
         <v>0.55000000000000004</v>
       </c>
-      <c r="S25" s="12">
+      <c r="S25" s="7">
         <v>0.56000000000000005</v>
       </c>
-      <c r="T25" s="12">
+      <c r="T25" s="7">
         <v>0.49</v>
       </c>
-      <c r="U25" s="12">
+      <c r="U25" s="7">
         <v>0.47</v>
       </c>
-      <c r="V25" s="12">
+      <c r="V25" s="7">
         <v>0.51</v>
       </c>
-      <c r="W25" s="12">
+      <c r="W25" s="7">
         <v>0.54</v>
       </c>
-      <c r="X25" s="12">
+      <c r="X25" s="7">
         <v>0.6</v>
       </c>
     </row>
@@ -13572,2299 +8586,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82139E5D-0C7E-EE46-9A6E-D6FE329CE0BC}">
-  <dimension ref="A1:V40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="25" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="8.25" customWidth="1"/>
-    <col min="2" max="2" width="7.625" customWidth="1"/>
-    <col min="4" max="4" width="9.375" customWidth="1"/>
-    <col min="5" max="5" width="7.375" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
-    <col min="8" max="8" width="8.875" customWidth="1"/>
-    <col min="9" max="9" width="33.125" customWidth="1"/>
-    <col min="10" max="21" width="9.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:22" ht="25" customHeight="1">
-      <c r="A1" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="J1" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="K1" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="M1" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="N1" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="O1" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="P1" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q1" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="R1" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="S1" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="T1" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="U1" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="V1" s="10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" ht="25" customHeight="1">
-      <c r="A2" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="17">
-        <v>1</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E2" s="17">
-        <v>1</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" s="21">
-        <v>2</v>
-      </c>
-      <c r="H2" s="17">
-        <v>2</v>
-      </c>
-      <c r="I2" s="17" t="str">
-        <f>_xlfn.TEXTJOIN({"","-","k-","-","-suppl:","-"},TRUE,"ml",G2,H2,A2,C2,D2)</f>
-        <v>ml2-2k-Czech-plurality-suppl:TRUE</v>
-      </c>
-      <c r="J2" s="18">
-        <v>0.94</v>
-      </c>
-      <c r="K2" s="18">
-        <v>0.86</v>
-      </c>
-      <c r="L2" s="18">
-        <v>0.91</v>
-      </c>
-      <c r="M2" s="18">
-        <v>0.88</v>
-      </c>
-      <c r="N2" s="18">
-        <v>0.83</v>
-      </c>
-      <c r="O2" s="18">
-        <v>0.89</v>
-      </c>
-      <c r="P2" s="18">
-        <v>0.9</v>
-      </c>
-      <c r="Q2" s="18">
-        <v>0.83</v>
-      </c>
-      <c r="R2" s="18">
-        <v>0.85</v>
-      </c>
-      <c r="S2" s="18">
-        <v>0.85</v>
-      </c>
-      <c r="T2" s="18">
-        <v>0.81</v>
-      </c>
-      <c r="U2" s="18">
-        <v>0.84</v>
-      </c>
-      <c r="V2" s="25">
-        <f t="shared" ref="V2:V5" si="0">_xlfn.LET(_xlpm.d,J2:T2,MAX(_xlpm.d))</f>
-        <v>0.94</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" ht="25" customHeight="1">
-      <c r="A3" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="17">
-        <v>1</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E3" s="17">
-        <v>1</v>
-      </c>
-      <c r="F3" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="21">
-        <v>2</v>
-      </c>
-      <c r="H3" s="17">
-        <v>1.2</v>
-      </c>
-      <c r="I3" s="17" t="str">
-        <f>_xlfn.TEXTJOIN({"","-","k-","-","-suppl:","-"},TRUE,"ml",G3,H3,A3,C3,D3)</f>
-        <v>ml2-1.2k-Czech-plurality-suppl:TRUE</v>
-      </c>
-      <c r="J3" s="18">
-        <v>0.87</v>
-      </c>
-      <c r="K3" s="18">
-        <v>0.83</v>
-      </c>
-      <c r="L3" s="18">
-        <v>0.86</v>
-      </c>
-      <c r="M3" s="18">
-        <v>0.86</v>
-      </c>
-      <c r="N3" s="18">
-        <v>0.84</v>
-      </c>
-      <c r="O3" s="18">
-        <v>0.82</v>
-      </c>
-      <c r="P3" s="18">
-        <v>0.89</v>
-      </c>
-      <c r="Q3" s="18">
-        <v>0.84</v>
-      </c>
-      <c r="R3" s="18">
-        <v>0.88</v>
-      </c>
-      <c r="S3" s="18">
-        <v>0.84</v>
-      </c>
-      <c r="T3" s="18">
-        <v>0.85</v>
-      </c>
-      <c r="U3" s="18">
-        <v>0.8</v>
-      </c>
-      <c r="V3" s="25">
-        <f t="shared" si="0"/>
-        <v>0.89</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" ht="25" customHeight="1">
-      <c r="A4" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="19">
-        <v>1</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E4" s="19">
-        <v>1</v>
-      </c>
-      <c r="F4" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" s="22">
-        <v>3</v>
-      </c>
-      <c r="H4" s="19">
-        <v>2</v>
-      </c>
-      <c r="I4" s="19" t="str">
-        <f>_xlfn.TEXTJOIN({"","-","k-","-","-suppl:","-"},TRUE,"ml",G4,H4,A4,C4,D4)</f>
-        <v>ml3-2k-Czech-plurality-suppl:TRUE</v>
-      </c>
-      <c r="J4" s="20">
-        <v>0.92</v>
-      </c>
-      <c r="K4" s="20">
-        <v>0.89</v>
-      </c>
-      <c r="L4" s="20">
-        <v>0.83</v>
-      </c>
-      <c r="M4" s="20">
-        <v>0.88</v>
-      </c>
-      <c r="N4" s="20">
-        <v>0.88</v>
-      </c>
-      <c r="O4" s="20">
-        <v>0.88</v>
-      </c>
-      <c r="P4" s="20">
-        <v>0.88</v>
-      </c>
-      <c r="Q4" s="20">
-        <v>0.88</v>
-      </c>
-      <c r="R4" s="20">
-        <v>0.89</v>
-      </c>
-      <c r="S4" s="20">
-        <v>0.84</v>
-      </c>
-      <c r="T4" s="20">
-        <v>0.86</v>
-      </c>
-      <c r="U4" s="20">
-        <v>0.87</v>
-      </c>
-      <c r="V4" s="26">
-        <f t="shared" si="0"/>
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" ht="25" customHeight="1">
-      <c r="A5" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="19">
-        <v>1</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" s="19">
-        <v>1</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="22">
-        <v>3</v>
-      </c>
-      <c r="H5" s="19">
-        <v>1.2</v>
-      </c>
-      <c r="I5" s="19" t="str">
-        <f>_xlfn.TEXTJOIN({"","-","k-","-","-suppl:","-"},TRUE,"ml",G5,H5,A5,C5,D5)</f>
-        <v>ml3-1.2k-Czech-plurality-suppl:TRUE</v>
-      </c>
-      <c r="J5" s="20">
-        <v>0.91</v>
-      </c>
-      <c r="K5" s="20">
-        <v>0.88</v>
-      </c>
-      <c r="L5" s="20">
-        <v>0.87</v>
-      </c>
-      <c r="M5" s="20">
-        <v>0.88</v>
-      </c>
-      <c r="N5" s="20">
-        <v>0.9</v>
-      </c>
-      <c r="O5" s="20">
-        <v>0.85</v>
-      </c>
-      <c r="P5" s="20">
-        <v>0.88</v>
-      </c>
-      <c r="Q5" s="20">
-        <v>0.87</v>
-      </c>
-      <c r="R5" s="20">
-        <v>0.86</v>
-      </c>
-      <c r="S5" s="20">
-        <v>0.86</v>
-      </c>
-      <c r="T5" s="20">
-        <v>0.85</v>
-      </c>
-      <c r="U5" s="20">
-        <v>0.82</v>
-      </c>
-      <c r="V5" s="26">
-        <f t="shared" si="0"/>
-        <v>0.91</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" ht="25" customHeight="1">
-      <c r="A6" s="11"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
-      <c r="N6" s="12"/>
-      <c r="O6" s="12"/>
-      <c r="P6" s="12"/>
-      <c r="Q6" s="12"/>
-      <c r="R6" s="12"/>
-      <c r="S6" s="12"/>
-      <c r="T6" s="13"/>
-    </row>
-    <row r="7" spans="1:22" ht="25" customHeight="1">
-      <c r="A7" s="11"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="12"/>
-      <c r="M7" s="12"/>
-      <c r="N7" s="12"/>
-      <c r="O7" s="12"/>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="12"/>
-      <c r="R7" s="12"/>
-      <c r="S7" s="12"/>
-      <c r="T7" s="13"/>
-    </row>
-    <row r="8" spans="1:22" ht="25" customHeight="1">
-      <c r="A8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" t="s">
-        <v>3</v>
-      </c>
-      <c r="G8" t="s">
-        <v>33</v>
-      </c>
-      <c r="H8" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" t="s">
-        <v>34</v>
-      </c>
-      <c r="J8" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="K8" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="L8" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="M8" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="N8" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="O8" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="P8" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q8" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="R8" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="S8" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="T8" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="U8" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="V8" s="12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" ht="25" customHeight="1">
-      <c r="A9" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="7">
-        <v>1</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E9" s="7">
-        <v>1</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" s="23">
-        <v>2</v>
-      </c>
-      <c r="H9" s="7">
-        <v>2</v>
-      </c>
-      <c r="I9" s="17" t="str">
-        <f>_xlfn.TEXTJOIN({"","-","k-","-","-suppl:","-"},TRUE,"ml",G9,H9,A9,C9,D9)</f>
-        <v>ml2-2k-Czech-plurality-suppl:FALSE</v>
-      </c>
-      <c r="J9" s="8">
-        <v>0.86</v>
-      </c>
-      <c r="K9" s="8">
-        <v>0.8</v>
-      </c>
-      <c r="L9" s="8">
-        <v>0.82</v>
-      </c>
-      <c r="M9" s="8">
-        <v>0.88</v>
-      </c>
-      <c r="N9" s="8">
-        <v>0.82</v>
-      </c>
-      <c r="O9" s="8">
-        <v>0.85</v>
-      </c>
-      <c r="P9" s="8">
-        <v>0.84</v>
-      </c>
-      <c r="Q9" s="8">
-        <v>0.79</v>
-      </c>
-      <c r="R9" s="8">
-        <v>0.82</v>
-      </c>
-      <c r="S9" s="8">
-        <v>0.84</v>
-      </c>
-      <c r="T9" s="8">
-        <v>0.82</v>
-      </c>
-      <c r="U9" s="8">
-        <v>0.88</v>
-      </c>
-      <c r="V9" s="25">
-        <f t="shared" ref="V9:V12" si="1">_xlfn.LET(_xlpm.d,J9:T9,MAX(_xlpm.d))</f>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" ht="25" customHeight="1">
-      <c r="A10" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="9">
-        <v>1</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="E10" s="9">
-        <v>1</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G10" s="24">
-        <v>3</v>
-      </c>
-      <c r="H10" s="9">
-        <v>2</v>
-      </c>
-      <c r="I10" s="9" t="str">
-        <f>_xlfn.TEXTJOIN({"","-","k-","-","-suppl:","-"},TRUE,"ml",G10,H10,A10,C10,D10)</f>
-        <v>ml3-2k-Czech-plurality-suppl:FALSE</v>
-      </c>
-      <c r="J10" s="1">
-        <v>0.84</v>
-      </c>
-      <c r="K10" s="1">
-        <v>0.83</v>
-      </c>
-      <c r="L10" s="1">
-        <v>0.77</v>
-      </c>
-      <c r="M10" s="1">
-        <v>0.86</v>
-      </c>
-      <c r="N10" s="1">
-        <v>0.87</v>
-      </c>
-      <c r="O10" s="1">
-        <v>0.85</v>
-      </c>
-      <c r="P10" s="1">
-        <v>0.83</v>
-      </c>
-      <c r="Q10" s="1">
-        <v>0.82</v>
-      </c>
-      <c r="R10" s="1">
-        <v>0.79</v>
-      </c>
-      <c r="S10" s="1">
-        <v>0.79</v>
-      </c>
-      <c r="T10" s="1">
-        <v>0.84</v>
-      </c>
-      <c r="U10" s="1">
-        <v>0.85</v>
-      </c>
-      <c r="V10" s="12">
-        <f t="shared" si="1"/>
-        <v>0.87</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" ht="25" customHeight="1">
-      <c r="A11" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="7">
-        <v>1</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" s="7">
-        <v>1</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G11" s="23">
-        <v>2</v>
-      </c>
-      <c r="H11" s="7">
-        <v>1.2</v>
-      </c>
-      <c r="I11" s="17" t="str">
-        <f>_xlfn.TEXTJOIN({"","-","k-","-","-suppl:","-"},TRUE,"ml",G11,H11,A11,C11,D11)</f>
-        <v>ml2-1.2k-Czech-plurality-suppl:FALSE</v>
-      </c>
-      <c r="J11" s="8">
-        <v>0.82</v>
-      </c>
-      <c r="K11" s="8">
-        <v>0.79</v>
-      </c>
-      <c r="L11" s="8">
-        <v>0.83</v>
-      </c>
-      <c r="M11" s="8">
-        <v>0.85</v>
-      </c>
-      <c r="N11" s="8">
-        <v>0.8</v>
-      </c>
-      <c r="O11" s="8">
-        <v>0.82</v>
-      </c>
-      <c r="P11" s="8">
-        <v>0.82</v>
-      </c>
-      <c r="Q11" s="8">
-        <v>0.79</v>
-      </c>
-      <c r="R11" s="8">
-        <v>0.8</v>
-      </c>
-      <c r="S11" s="8">
-        <v>0.82</v>
-      </c>
-      <c r="T11" s="8">
-        <v>0.86</v>
-      </c>
-      <c r="U11" s="8">
-        <v>0.81</v>
-      </c>
-      <c r="V11" s="27">
-        <f t="shared" si="1"/>
-        <v>0.86</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" ht="25" customHeight="1">
-      <c r="A12" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="9">
-        <v>1</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="9">
-        <v>1</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G12" s="24">
-        <v>3</v>
-      </c>
-      <c r="H12" s="9">
-        <v>1.2</v>
-      </c>
-      <c r="I12" s="9" t="str">
-        <f>_xlfn.TEXTJOIN({"","-","k-","-","-suppl:","-"},TRUE,"ml",G12,H12,A12,C12,D12)</f>
-        <v>ml3-1.2k-Czech-plurality-suppl:FALSE</v>
-      </c>
-      <c r="J12" s="1">
-        <v>0.88</v>
-      </c>
-      <c r="K12" s="1">
-        <v>0.78</v>
-      </c>
-      <c r="L12" s="1">
-        <v>0.82</v>
-      </c>
-      <c r="M12" s="1">
-        <v>0.85</v>
-      </c>
-      <c r="N12" s="1">
-        <v>0.86</v>
-      </c>
-      <c r="O12" s="1">
-        <v>0.85</v>
-      </c>
-      <c r="P12" s="1">
-        <v>0.84</v>
-      </c>
-      <c r="Q12" s="1">
-        <v>0.83</v>
-      </c>
-      <c r="R12" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="S12" s="1">
-        <v>0.85</v>
-      </c>
-      <c r="T12" s="1">
-        <v>0.84</v>
-      </c>
-      <c r="U12" s="1">
-        <v>0.87</v>
-      </c>
-      <c r="V12" s="12">
-        <f t="shared" si="1"/>
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" ht="25" customHeight="1">
-      <c r="A13" s="11"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="12"/>
-      <c r="M13" s="12"/>
-      <c r="N13" s="12"/>
-      <c r="O13" s="12"/>
-      <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="12"/>
-      <c r="S13" s="12"/>
-      <c r="T13" s="13"/>
-    </row>
-    <row r="14" spans="1:22" ht="25" customHeight="1">
-      <c r="A14" s="14"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
-      <c r="P14" s="1"/>
-      <c r="Q14" s="1"/>
-      <c r="R14" s="1"/>
-      <c r="S14" s="1"/>
-      <c r="T14" s="15"/>
-    </row>
-    <row r="15" spans="1:22" ht="25" customHeight="1">
-      <c r="A15" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="J15" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="K15" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="L15" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="M15" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="N15" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="O15" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="P15" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q15" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="R15" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="S15" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="T15" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="U15" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="V15" s="16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" ht="25" customHeight="1">
-      <c r="A16" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="7">
-        <v>2</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D16" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="E16" s="7">
-        <v>1</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G16" s="23">
-        <v>2</v>
-      </c>
-      <c r="H16" s="7">
-        <v>2</v>
-      </c>
-      <c r="I16" s="17" t="str">
-        <f>_xlfn.TEXTJOIN({"","-","k-","-","-suppl:","-"},TRUE,"ml",G16,H16,A16,C16,D16)</f>
-        <v>ml2-2k-Czech-gender-suppl:TRUE</v>
-      </c>
-      <c r="J16" s="8">
-        <v>0.62</v>
-      </c>
-      <c r="K16" s="8">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="L16" s="8">
-        <v>0.62</v>
-      </c>
-      <c r="M16" s="8">
-        <v>0.62</v>
-      </c>
-      <c r="N16" s="8">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="O16" s="8">
-        <v>0.69</v>
-      </c>
-      <c r="P16" s="8">
-        <v>0.64</v>
-      </c>
-      <c r="Q16" s="8">
-        <v>0.6</v>
-      </c>
-      <c r="R16" s="8">
-        <v>0.54</v>
-      </c>
-      <c r="S16" s="8">
-        <v>0.61</v>
-      </c>
-      <c r="T16" s="8">
-        <v>0.68</v>
-      </c>
-      <c r="U16" s="8">
-        <v>0.6</v>
-      </c>
-      <c r="V16" s="25">
-        <f t="shared" ref="V16:V19" si="2">_xlfn.LET(_xlpm.d,J16:T16,MAX(_xlpm.d))</f>
-        <v>0.69</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" ht="25" customHeight="1">
-      <c r="A17" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="7">
-        <v>2</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D17" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" s="7">
-        <v>1</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G17" s="23">
-        <v>2</v>
-      </c>
-      <c r="H17" s="7">
-        <v>1.2</v>
-      </c>
-      <c r="I17" s="7" t="str">
-        <f>_xlfn.TEXTJOIN({"","-","k-","-","-suppl:","-"},TRUE,"ml",G17,H17,A17,C17,D17)</f>
-        <v>ml2-1.2k-Czech-gender-suppl:TRUE</v>
-      </c>
-      <c r="J17" s="8">
-        <v>0.62</v>
-      </c>
-      <c r="K17" s="8">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="L17" s="8">
-        <v>0.62</v>
-      </c>
-      <c r="M17" s="8">
-        <v>0.62</v>
-      </c>
-      <c r="N17" s="8">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="O17" s="8">
-        <v>0.69</v>
-      </c>
-      <c r="P17" s="8">
-        <v>0.64</v>
-      </c>
-      <c r="Q17" s="8">
-        <v>0.6</v>
-      </c>
-      <c r="R17" s="8">
-        <v>0.54</v>
-      </c>
-      <c r="S17" s="8">
-        <v>0.61</v>
-      </c>
-      <c r="T17" s="8">
-        <v>0.68</v>
-      </c>
-      <c r="U17" s="8">
-        <v>0.6</v>
-      </c>
-      <c r="V17" s="27">
-        <f t="shared" si="2"/>
-        <v>0.69</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" ht="25" customHeight="1">
-      <c r="A18" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="9">
-        <v>2</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D18" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" s="9">
-        <v>1</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G18" s="24">
-        <v>3</v>
-      </c>
-      <c r="H18" s="9">
-        <v>2</v>
-      </c>
-      <c r="I18" s="9" t="str">
-        <f>_xlfn.TEXTJOIN({"","-","k-","-","-suppl:","-"},TRUE,"ml",G18,H18,A18,C18,D18)</f>
-        <v>ml3-2k-Czech-gender-suppl:TRUE</v>
-      </c>
-      <c r="J18" s="1">
-        <v>0.7</v>
-      </c>
-      <c r="K18" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="L18" s="1">
-        <v>0.7</v>
-      </c>
-      <c r="M18" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="N18" s="1">
-        <v>0.68</v>
-      </c>
-      <c r="O18" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="P18" s="1">
-        <v>0.71</v>
-      </c>
-      <c r="Q18" s="1">
-        <v>0.71</v>
-      </c>
-      <c r="R18" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="S18" s="1">
-        <v>0.68</v>
-      </c>
-      <c r="T18" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="U18" s="1">
-        <v>0.69</v>
-      </c>
-      <c r="V18" s="12">
-        <f t="shared" si="2"/>
-        <v>0.71</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22" ht="25" customHeight="1">
-      <c r="A19" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19" s="9">
-        <v>2</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="E19" s="9">
-        <v>1</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G19" s="24">
-        <v>3</v>
-      </c>
-      <c r="H19" s="9">
-        <v>1.2</v>
-      </c>
-      <c r="I19" s="9" t="str">
-        <f>_xlfn.TEXTJOIN({"","-","k-","-","-suppl:","-"},TRUE,"ml",G19,H19,A19,C19,D19)</f>
-        <v>ml3-1.2k-Czech-gender-suppl:TRUE</v>
-      </c>
-      <c r="J19" s="1">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="K19" s="1">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="L19" s="1">
-        <v>0.68</v>
-      </c>
-      <c r="M19" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="N19" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="O19" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="P19" s="1">
-        <v>0.7</v>
-      </c>
-      <c r="Q19" s="1">
-        <v>0.68</v>
-      </c>
-      <c r="R19" s="1">
-        <v>0.69</v>
-      </c>
-      <c r="S19" s="1">
-        <v>0.71</v>
-      </c>
-      <c r="T19" s="1">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="U19" s="1">
-        <v>0.51</v>
-      </c>
-      <c r="V19" s="12">
-        <f t="shared" si="2"/>
-        <v>0.71</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" ht="25" customHeight="1">
-      <c r="A20" s="11"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="12"/>
-      <c r="K20" s="12"/>
-      <c r="L20" s="12"/>
-      <c r="M20" s="12"/>
-      <c r="N20" s="12"/>
-      <c r="O20" s="12"/>
-      <c r="P20" s="12"/>
-      <c r="Q20" s="12"/>
-      <c r="R20" s="12"/>
-      <c r="S20" s="12"/>
-      <c r="T20" s="13"/>
-    </row>
-    <row r="21" spans="1:22" ht="25" customHeight="1">
-      <c r="A21" s="11"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
-      <c r="K21" s="12"/>
-      <c r="L21" s="12"/>
-      <c r="M21" s="12"/>
-      <c r="N21" s="12"/>
-      <c r="O21" s="12"/>
-      <c r="P21" s="12"/>
-      <c r="Q21" s="12"/>
-      <c r="R21" s="12"/>
-      <c r="S21" s="12"/>
-      <c r="T21" s="13"/>
-    </row>
-    <row r="22" spans="1:22" ht="25" customHeight="1">
-      <c r="A22" t="s">
-        <v>0</v>
-      </c>
-      <c r="B22" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D22" t="s">
-        <v>2</v>
-      </c>
-      <c r="E22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F22" t="s">
-        <v>3</v>
-      </c>
-      <c r="G22" t="s">
-        <v>33</v>
-      </c>
-      <c r="H22" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" t="s">
-        <v>34</v>
-      </c>
-      <c r="J22" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="K22" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="L22" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="M22" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="N22" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="O22" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="P22" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q22" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="R22" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="S22" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="T22" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="U22" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="V22" s="12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22" ht="25" customHeight="1">
-      <c r="A23" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B23" s="7">
-        <v>2</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D23" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E23" s="7">
-        <v>1</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G23" s="23">
-        <v>2</v>
-      </c>
-      <c r="H23" s="7">
-        <v>2</v>
-      </c>
-      <c r="I23" s="17" t="str">
-        <f>_xlfn.TEXTJOIN({"","-","k-","-","-suppl:","-"},TRUE,"ml",G23,H23,A23,C23,D23)</f>
-        <v>ml2-2k-Czech-gender-suppl:FALSE</v>
-      </c>
-      <c r="J23" s="8">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="K23" s="8">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="L23" s="8">
-        <v>0.65</v>
-      </c>
-      <c r="M23" s="8">
-        <v>0.62</v>
-      </c>
-      <c r="N23" s="8">
-        <v>0.6</v>
-      </c>
-      <c r="O23" s="8">
-        <v>0.65</v>
-      </c>
-      <c r="P23" s="8">
-        <v>0.66</v>
-      </c>
-      <c r="Q23" s="8">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="R23" s="8">
-        <v>0.53</v>
-      </c>
-      <c r="S23" s="8">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="T23" s="8">
-        <v>0.7</v>
-      </c>
-      <c r="U23" s="8">
-        <v>0.6</v>
-      </c>
-      <c r="V23" s="25">
-        <f t="shared" ref="V23:V26" si="3">_xlfn.LET(_xlpm.d,J23:T23,MAX(_xlpm.d))</f>
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22" ht="25" customHeight="1">
-      <c r="A24" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B24" s="7">
-        <v>2</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D24" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E24" s="7">
-        <v>1</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G24" s="23">
-        <v>2</v>
-      </c>
-      <c r="H24" s="7">
-        <v>1.2</v>
-      </c>
-      <c r="I24" s="7" t="str">
-        <f>_xlfn.TEXTJOIN({"","-","k-","-","-suppl:","-"},TRUE,"ml",G24,H24,A24,C24,D24)</f>
-        <v>ml2-1.2k-Czech-gender-suppl:FALSE</v>
-      </c>
-      <c r="J24" s="8">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="K24" s="8">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="L24" s="8">
-        <v>0.65</v>
-      </c>
-      <c r="M24" s="8">
-        <v>0.62</v>
-      </c>
-      <c r="N24" s="8">
-        <v>0.6</v>
-      </c>
-      <c r="O24" s="8">
-        <v>0.65</v>
-      </c>
-      <c r="P24" s="8">
-        <v>0.66</v>
-      </c>
-      <c r="Q24" s="8">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="R24" s="8">
-        <v>0.53</v>
-      </c>
-      <c r="S24" s="8">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="T24" s="8">
-        <v>0.7</v>
-      </c>
-      <c r="U24" s="8">
-        <v>0.6</v>
-      </c>
-      <c r="V24" s="27">
-        <f t="shared" si="3"/>
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22" ht="25" customHeight="1">
-      <c r="A25" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B25" s="9">
-        <v>2</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D25" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="E25" s="9">
-        <v>1</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G25" s="24">
-        <v>3</v>
-      </c>
-      <c r="H25" s="9">
-        <v>2</v>
-      </c>
-      <c r="I25" s="9" t="str">
-        <f>_xlfn.TEXTJOIN({"","-","k-","-","-suppl:","-"},TRUE,"ml",G25,H25,A25,C25,D25)</f>
-        <v>ml3-2k-Czech-gender-suppl:FALSE</v>
-      </c>
-      <c r="J25" s="1">
-        <v>0.68</v>
-      </c>
-      <c r="K25" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="L25" s="1">
-        <v>0.69</v>
-      </c>
-      <c r="M25" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="N25" s="1">
-        <v>0.67</v>
-      </c>
-      <c r="O25" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="P25" s="1">
-        <v>0.68</v>
-      </c>
-      <c r="Q25" s="1">
-        <v>0.73</v>
-      </c>
-      <c r="R25" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="S25" s="1">
-        <v>0.7</v>
-      </c>
-      <c r="T25" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="U25" s="1">
-        <v>0.69</v>
-      </c>
-      <c r="V25" s="12">
-        <f t="shared" si="3"/>
-        <v>0.73</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22" ht="25" customHeight="1">
-      <c r="A26" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B26" s="9">
-        <v>2</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D26" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="9">
-        <v>1</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G26" s="24">
-        <v>3</v>
-      </c>
-      <c r="H26" s="9">
-        <v>1.2</v>
-      </c>
-      <c r="I26" s="9" t="str">
-        <f>_xlfn.TEXTJOIN({"","-","k-","-","-suppl:","-"},TRUE,"ml",G26,H26,A26,C26,D26)</f>
-        <v>ml3-1.2k-Czech-gender-suppl:FALSE</v>
-      </c>
-      <c r="J26" s="1">
-        <v>0.53</v>
-      </c>
-      <c r="K26" s="1">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="L26" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="M26" s="1">
-        <v>0.61</v>
-      </c>
-      <c r="N26" s="1">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="O26" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="P26" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="Q26" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="R26" s="1">
-        <v>0.68</v>
-      </c>
-      <c r="S26" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="T26" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="U26" s="1">
-        <v>0.53</v>
-      </c>
-      <c r="V26" s="12">
-        <f t="shared" si="3"/>
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22" ht="25" customHeight="1">
-      <c r="A27" s="11"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
-      <c r="M27" s="12"/>
-      <c r="N27" s="12"/>
-      <c r="O27" s="12"/>
-      <c r="P27" s="12"/>
-      <c r="Q27" s="12"/>
-      <c r="R27" s="12"/>
-      <c r="S27" s="12"/>
-      <c r="T27" s="13"/>
-    </row>
-    <row r="28" spans="1:22" ht="25" customHeight="1">
-      <c r="A28" s="14"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-      <c r="P28" s="1"/>
-      <c r="Q28" s="1"/>
-      <c r="R28" s="1"/>
-      <c r="S28" s="1"/>
-      <c r="T28" s="15"/>
-    </row>
-    <row r="29" spans="1:22" ht="25" customHeight="1">
-      <c r="A29" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B29" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="I29" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="J29" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="K29" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="L29" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="M29" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="N29" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="O29" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="P29" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q29" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="R29" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="S29" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="T29" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="U29" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="V29" s="16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22" ht="25" customHeight="1">
-      <c r="A30" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B30" s="7">
-        <v>3</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D30" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="E30" s="7">
-        <v>1</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G30" s="23">
-        <v>2</v>
-      </c>
-      <c r="H30" s="7">
-        <v>2</v>
-      </c>
-      <c r="I30" s="17" t="str">
-        <f>_xlfn.TEXTJOIN({"","-","k-","-","-suppl:","-"},TRUE,"ml",G30,H30,A30,C30,D30)</f>
-        <v>ml2-2k-Czech-case-suppl:TRUE</v>
-      </c>
-      <c r="J30" s="8">
-        <v>0.59</v>
-      </c>
-      <c r="K30" s="8">
-        <v>0.38</v>
-      </c>
-      <c r="L30" s="8">
-        <v>0.51</v>
-      </c>
-      <c r="M30" s="8">
-        <v>0.47</v>
-      </c>
-      <c r="N30" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="O30" s="8">
-        <v>0.4</v>
-      </c>
-      <c r="P30" s="8">
-        <v>0.54</v>
-      </c>
-      <c r="Q30" s="8">
-        <v>0.48</v>
-      </c>
-      <c r="R30" s="8">
-        <v>0.52</v>
-      </c>
-      <c r="S30" s="8">
-        <v>0.52</v>
-      </c>
-      <c r="T30" s="8">
-        <v>0.47</v>
-      </c>
-      <c r="U30" s="8">
-        <v>0.44</v>
-      </c>
-      <c r="V30" s="25">
-        <f t="shared" ref="V30:V33" si="4">_xlfn.LET(_xlpm.d,J30:T30,MAX(_xlpm.d))</f>
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22" ht="25" customHeight="1">
-      <c r="A31" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B31" s="7">
-        <v>3</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D31" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="E31" s="7">
-        <v>1</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G31" s="23">
-        <v>2</v>
-      </c>
-      <c r="H31" s="7">
-        <v>1.2</v>
-      </c>
-      <c r="I31" s="17" t="str">
-        <f>_xlfn.TEXTJOIN({"","-","k-","-","-suppl:","-"},TRUE,"ml",G31,H31,A31,C31,D31)</f>
-        <v>ml2-1.2k-Czech-case-suppl:TRUE</v>
-      </c>
-      <c r="J31" s="8">
-        <v>0.59</v>
-      </c>
-      <c r="K31" s="8">
-        <v>0.38</v>
-      </c>
-      <c r="L31" s="8">
-        <v>0.51</v>
-      </c>
-      <c r="M31" s="8">
-        <v>0.47</v>
-      </c>
-      <c r="N31" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="O31" s="8">
-        <v>0.4</v>
-      </c>
-      <c r="P31" s="8">
-        <v>0.54</v>
-      </c>
-      <c r="Q31" s="8">
-        <v>0.48</v>
-      </c>
-      <c r="R31" s="8">
-        <v>0.52</v>
-      </c>
-      <c r="S31" s="8">
-        <v>0.52</v>
-      </c>
-      <c r="T31" s="8">
-        <v>0.47</v>
-      </c>
-      <c r="U31" s="8">
-        <v>0.44</v>
-      </c>
-      <c r="V31" s="27">
-        <f t="shared" si="4"/>
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22" ht="25" customHeight="1">
-      <c r="A32" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B32" s="9">
-        <v>3</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D32" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="E32" s="9">
-        <v>1</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G32" s="24">
-        <v>3</v>
-      </c>
-      <c r="H32" s="9">
-        <v>2</v>
-      </c>
-      <c r="I32" s="9" t="str">
-        <f>_xlfn.TEXTJOIN({"","-","k-","-","-suppl:","-"},TRUE,"ml",G32,H32,A32,C32,D32)</f>
-        <v>ml3-2k-Czech-case-suppl:TRUE</v>
-      </c>
-      <c r="J32" s="1">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="K32" s="1">
-        <v>0.53</v>
-      </c>
-      <c r="L32" s="1">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="M32" s="1">
-        <v>0.48</v>
-      </c>
-      <c r="N32" s="1">
-        <v>0.49</v>
-      </c>
-      <c r="O32" s="1">
-        <v>0.51</v>
-      </c>
-      <c r="P32" s="1">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="Q32" s="1">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="R32" s="1">
-        <v>0.59</v>
-      </c>
-      <c r="S32" s="1">
-        <v>0.54</v>
-      </c>
-      <c r="T32" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="U32" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="V32" s="12">
-        <f t="shared" si="4"/>
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="33" spans="1:22" ht="25" customHeight="1">
-      <c r="A33" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B33" s="9">
-        <v>3</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D33" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="E33" s="9">
-        <v>1</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G33" s="24">
-        <v>3</v>
-      </c>
-      <c r="H33" s="9">
-        <v>1.2</v>
-      </c>
-      <c r="I33" s="9" t="str">
-        <f>_xlfn.TEXTJOIN({"","-","k-","-","-suppl:","-"},TRUE,"ml",G33,H33,A33,C33,D33)</f>
-        <v>ml3-1.2k-Czech-case-suppl:TRUE</v>
-      </c>
-      <c r="J33" s="1">
-        <v>0.45</v>
-      </c>
-      <c r="K33" s="1">
-        <v>0.54</v>
-      </c>
-      <c r="L33" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="M33" s="1">
-        <v>0.49</v>
-      </c>
-      <c r="N33" s="1">
-        <v>0.47</v>
-      </c>
-      <c r="O33" s="1">
-        <v>0.47</v>
-      </c>
-      <c r="P33" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="Q33" s="1">
-        <v>0.46</v>
-      </c>
-      <c r="R33" s="1">
-        <v>0.53</v>
-      </c>
-      <c r="S33" s="1">
-        <v>0.43</v>
-      </c>
-      <c r="T33" s="1">
-        <v>0.45</v>
-      </c>
-      <c r="U33" s="1">
-        <v>0.51</v>
-      </c>
-      <c r="V33" s="12">
-        <f t="shared" si="4"/>
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="34" spans="1:22" ht="25" customHeight="1">
-      <c r="A34" s="11"/>
-      <c r="I34" s="12"/>
-      <c r="J34" s="12"/>
-      <c r="K34" s="12"/>
-      <c r="L34" s="12"/>
-      <c r="M34" s="12"/>
-      <c r="N34" s="12"/>
-      <c r="O34" s="12"/>
-      <c r="P34" s="12"/>
-      <c r="Q34" s="12"/>
-      <c r="R34" s="12"/>
-      <c r="S34" s="12"/>
-      <c r="T34" s="13"/>
-    </row>
-    <row r="35" spans="1:22" ht="25" customHeight="1">
-      <c r="A35" s="11"/>
-      <c r="I35" s="12"/>
-      <c r="J35" s="12"/>
-      <c r="K35" s="12"/>
-      <c r="L35" s="12"/>
-      <c r="M35" s="12"/>
-      <c r="N35" s="12"/>
-      <c r="O35" s="12"/>
-      <c r="P35" s="12"/>
-      <c r="Q35" s="12"/>
-      <c r="R35" s="12"/>
-      <c r="S35" s="12"/>
-      <c r="T35" s="13"/>
-    </row>
-    <row r="36" spans="1:22" ht="25" customHeight="1">
-      <c r="A36" t="s">
-        <v>0</v>
-      </c>
-      <c r="B36" t="s">
-        <v>23</v>
-      </c>
-      <c r="C36" t="s">
-        <v>1</v>
-      </c>
-      <c r="D36" t="s">
-        <v>2</v>
-      </c>
-      <c r="E36" t="s">
-        <v>24</v>
-      </c>
-      <c r="F36" t="s">
-        <v>3</v>
-      </c>
-      <c r="G36" t="s">
-        <v>33</v>
-      </c>
-      <c r="H36" t="s">
-        <v>32</v>
-      </c>
-      <c r="I36" t="s">
-        <v>34</v>
-      </c>
-      <c r="J36" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="K36" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="L36" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="M36" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="N36" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="O36" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="P36" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q36" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="R36" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="S36" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="T36" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="U36" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="V36" s="12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="37" spans="1:22" ht="25" customHeight="1">
-      <c r="A37" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B37" s="7">
-        <v>3</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D37" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E37" s="7">
-        <v>1</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G37" s="23">
-        <v>2</v>
-      </c>
-      <c r="H37" s="7">
-        <v>2</v>
-      </c>
-      <c r="I37" s="17" t="str">
-        <f>_xlfn.TEXTJOIN({"","-","k-","-","-suppl:","-"},TRUE,"ml",G37,H37,A37,C37,D37)</f>
-        <v>ml2-2k-Czech-case-suppl:FALSE</v>
-      </c>
-      <c r="J37" s="8">
-        <v>0.47</v>
-      </c>
-      <c r="K37" s="8">
-        <v>0.37</v>
-      </c>
-      <c r="L37" s="8">
-        <v>0.45</v>
-      </c>
-      <c r="M37" s="8">
-        <v>0.43</v>
-      </c>
-      <c r="N37" s="8">
-        <v>0.47</v>
-      </c>
-      <c r="O37" s="8">
-        <v>0.36</v>
-      </c>
-      <c r="P37" s="8">
-        <v>0.45</v>
-      </c>
-      <c r="Q37" s="8">
-        <v>0.38</v>
-      </c>
-      <c r="R37" s="8">
-        <v>0.43</v>
-      </c>
-      <c r="S37" s="8">
-        <v>0.45</v>
-      </c>
-      <c r="T37" s="8">
-        <v>0.42</v>
-      </c>
-      <c r="U37" s="8">
-        <v>0.36</v>
-      </c>
-      <c r="V37" s="25">
-        <f t="shared" ref="V37:V40" si="5">_xlfn.LET(_xlpm.d,J37:T37,MAX(_xlpm.d))</f>
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="38" spans="1:22" ht="25" customHeight="1">
-      <c r="A38" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B38" s="7">
-        <v>3</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D38" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E38" s="7">
-        <v>1</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G38" s="23">
-        <v>2</v>
-      </c>
-      <c r="H38" s="7">
-        <v>1.2</v>
-      </c>
-      <c r="I38" s="17" t="str">
-        <f>_xlfn.TEXTJOIN({"","-","k-","-","-suppl:","-"},TRUE,"ml",G38,H38,A38,C38,D38)</f>
-        <v>ml2-1.2k-Czech-case-suppl:FALSE</v>
-      </c>
-      <c r="J38" s="8">
-        <v>0.47</v>
-      </c>
-      <c r="K38" s="8">
-        <v>0.37</v>
-      </c>
-      <c r="L38" s="8">
-        <v>0.45</v>
-      </c>
-      <c r="M38" s="8">
-        <v>0.43</v>
-      </c>
-      <c r="N38" s="8">
-        <v>0.47</v>
-      </c>
-      <c r="O38" s="8">
-        <v>0.36</v>
-      </c>
-      <c r="P38" s="8">
-        <v>0.45</v>
-      </c>
-      <c r="Q38" s="8">
-        <v>0.38</v>
-      </c>
-      <c r="R38" s="8">
-        <v>0.43</v>
-      </c>
-      <c r="S38" s="8">
-        <v>0.45</v>
-      </c>
-      <c r="T38" s="8">
-        <v>0.42</v>
-      </c>
-      <c r="U38" s="8">
-        <v>0.36</v>
-      </c>
-      <c r="V38" s="27">
-        <f t="shared" si="5"/>
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="39" spans="1:22" ht="25" customHeight="1">
-      <c r="A39" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B39" s="9">
-        <v>3</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D39" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="E39" s="9">
-        <v>1</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G39" s="24">
-        <v>3</v>
-      </c>
-      <c r="H39" s="9">
-        <v>2</v>
-      </c>
-      <c r="I39" s="9" t="str">
-        <f>_xlfn.TEXTJOIN({"","-","k-","-","-suppl:","-"},TRUE,"ml",G39,H39,A39,C39,D39)</f>
-        <v>ml3-2k-Czech-case-suppl:FALSE</v>
-      </c>
-      <c r="J39" s="1">
-        <v>0.43</v>
-      </c>
-      <c r="K39" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="L39" s="1">
-        <v>0.49</v>
-      </c>
-      <c r="M39" s="1">
-        <v>0.44</v>
-      </c>
-      <c r="N39" s="1">
-        <v>0.46</v>
-      </c>
-      <c r="O39" s="1">
-        <v>0.45</v>
-      </c>
-      <c r="P39" s="1">
-        <v>0.49</v>
-      </c>
-      <c r="Q39" s="1">
-        <v>0.44</v>
-      </c>
-      <c r="R39" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="S39" s="1">
-        <v>0.49</v>
-      </c>
-      <c r="T39" s="1">
-        <v>0.46</v>
-      </c>
-      <c r="U39" s="1">
-        <v>0.49</v>
-      </c>
-      <c r="V39" s="12">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:22" ht="25" customHeight="1">
-      <c r="A40" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B40" s="9">
-        <v>3</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D40" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="E40" s="9">
-        <v>1</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G40" s="24">
-        <v>3</v>
-      </c>
-      <c r="H40" s="9">
-        <v>1.2</v>
-      </c>
-      <c r="I40" s="9" t="str">
-        <f>_xlfn.TEXTJOIN({"","-","k-","-","-suppl:","-"},TRUE,"ml",G40,H40,A40,C40,D40)</f>
-        <v>ml3-1.2k-Czech-case-suppl:FALSE</v>
-      </c>
-      <c r="J40" s="1">
-        <v>0.36</v>
-      </c>
-      <c r="K40" s="1">
-        <v>0.42</v>
-      </c>
-      <c r="L40" s="1">
-        <v>0.47</v>
-      </c>
-      <c r="M40" s="1">
-        <v>0.39</v>
-      </c>
-      <c r="N40" s="1">
-        <v>0.44</v>
-      </c>
-      <c r="O40" s="1">
-        <v>0.45</v>
-      </c>
-      <c r="P40" s="1">
-        <v>0.38</v>
-      </c>
-      <c r="Q40" s="1">
-        <v>0.35</v>
-      </c>
-      <c r="R40" s="1">
-        <v>0.42</v>
-      </c>
-      <c r="S40" s="1">
-        <v>0.41</v>
-      </c>
-      <c r="T40" s="1">
-        <v>0.39</v>
-      </c>
-      <c r="U40" s="1">
-        <v>0.48</v>
-      </c>
-      <c r="V40" s="12">
-        <f t="shared" si="5"/>
-        <v>0.47</v>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="I6:T7 I13:T14 I20:T21 I27:T28 I34:T35 J2:V5 J8:V12 J15:V19 J22:V26 J29:V33 J36:V40">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="num" val="1"/>
-        <color theme="4" tint="0.59999389629810485"/>
-        <color theme="0"/>
-        <color rgb="FFFFC000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <tableParts count="6">
-    <tablePart r:id="rId2"/>
-    <tablePart r:id="rId3"/>
-    <tablePart r:id="rId4"/>
-    <tablePart r:id="rId5"/>
-    <tablePart r:id="rId6"/>
-    <tablePart r:id="rId7"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DC72E40-885E-3A4F-84F6-67339B580D57}">
   <dimension ref="A1:S28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="25" customHeight="1"/>
@@ -17515,7 +10236,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{191055A3-ED0D-8042-AE2F-2AB0F1AC6A90}">
   <dimension ref="A1:S42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="25" customHeight="1"/>
@@ -19874,7 +12595,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91308589-3A5F-894D-9477-8620D1A5FD56}">
   <dimension ref="A1:S39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="27" customHeight="1"/>
@@ -21682,7 +14403,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C603AA5-E025-F347-8D4B-F2B6715A9644}">
   <dimension ref="A1:S42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="25" customHeight="1"/>
